--- a/data/stocks_20260409_111433.xlsx
+++ b/data/stocks_20260409_111433.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="股票池" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W70"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1119,69 +1119,69 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>688041</v>
+        <v>300502</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>227</v>
+        <v>490</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.66</v>
+        <v>-2.29</v>
       </c>
       <c r="E10" t="n">
-        <v>219.96</v>
+        <v>470.6</v>
       </c>
       <c r="F10" t="n">
-        <v>218.58</v>
+        <v>461.92</v>
       </c>
       <c r="G10" t="n">
-        <v>221.63</v>
+        <v>447.38</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.211</v>
+        <v>19.834</v>
       </c>
       <c r="I10" t="n">
-        <v>-7.103</v>
+        <v>17.004</v>
       </c>
       <c r="J10" t="n">
-        <v>63.95</v>
+        <v>67.37</v>
       </c>
       <c r="K10" t="n">
-        <v>52.72</v>
+        <v>56.45</v>
       </c>
       <c r="L10" t="n">
-        <v>86.42</v>
+        <v>89.22</v>
       </c>
       <c r="M10" t="n">
-        <v>61.83</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>51.6</v>
+        <v>62.69</v>
       </c>
       <c r="O10" t="n">
-        <v>48.35</v>
+        <v>59.15</v>
       </c>
       <c r="P10" t="n">
-        <v>1963.61</v>
+        <v>2984.16</v>
       </c>
       <c r="Q10" t="n">
-        <v>1842.92</v>
+        <v>3986.13</v>
       </c>
       <c r="R10" t="n">
-        <v>1.07</v>
+        <v>0.75</v>
       </c>
       <c r="S10" t="n">
-        <v>225</v>
+        <v>491.3</v>
       </c>
       <c r="T10" t="n">
-        <v>230.36</v>
+        <v>497.8</v>
       </c>
       <c r="U10" t="n">
-        <v>223.66</v>
+        <v>488</v>
       </c>
       <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
@@ -1192,69 +1192,69 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>300502</v>
+        <v>300394</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>490</v>
+        <v>346.9</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.29</v>
+        <v>2.94</v>
       </c>
       <c r="E11" t="n">
-        <v>470.6</v>
+        <v>331.58</v>
       </c>
       <c r="F11" t="n">
-        <v>461.92</v>
+        <v>325.23</v>
       </c>
       <c r="G11" t="n">
-        <v>447.38</v>
+        <v>317.05</v>
       </c>
       <c r="H11" t="n">
-        <v>19.834</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>17.004</v>
+        <v>7.34</v>
       </c>
       <c r="J11" t="n">
-        <v>67.37</v>
+        <v>71.48</v>
       </c>
       <c r="K11" t="n">
-        <v>56.45</v>
+        <v>65.69</v>
       </c>
       <c r="L11" t="n">
-        <v>89.22</v>
+        <v>83.06</v>
       </c>
       <c r="M11" t="n">
-        <v>65.81999999999999</v>
+        <v>64.95</v>
       </c>
       <c r="N11" t="n">
-        <v>62.69</v>
+        <v>59.49</v>
       </c>
       <c r="O11" t="n">
-        <v>59.15</v>
+        <v>57.96</v>
       </c>
       <c r="P11" t="n">
-        <v>2984.16</v>
+        <v>4849.02</v>
       </c>
       <c r="Q11" t="n">
-        <v>3986.13</v>
+        <v>3553.49</v>
       </c>
       <c r="R11" t="n">
-        <v>0.75</v>
+        <v>1.36</v>
       </c>
       <c r="S11" t="n">
-        <v>491.3</v>
+        <v>337.02</v>
       </c>
       <c r="T11" t="n">
-        <v>497.8</v>
+        <v>359.71</v>
       </c>
       <c r="U11" t="n">
-        <v>488</v>
+        <v>331.13</v>
       </c>
       <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
@@ -1265,69 +1265,69 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>300394</v>
+        <v>988</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>华工科技</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>346.9</v>
+        <v>114.93</v>
       </c>
       <c r="D12" t="n">
-        <v>2.94</v>
+        <v>4.09</v>
       </c>
       <c r="E12" t="n">
-        <v>331.58</v>
+        <v>106.68</v>
       </c>
       <c r="F12" t="n">
-        <v>325.23</v>
+        <v>106.35</v>
       </c>
       <c r="G12" t="n">
-        <v>317.05</v>
+        <v>111.52</v>
       </c>
       <c r="H12" t="n">
-        <v>8.699999999999999</v>
+        <v>1.885</v>
       </c>
       <c r="I12" t="n">
-        <v>7.34</v>
+        <v>2.961</v>
       </c>
       <c r="J12" t="n">
-        <v>71.48</v>
+        <v>56.01</v>
       </c>
       <c r="K12" t="n">
-        <v>65.69</v>
+        <v>35.19</v>
       </c>
       <c r="L12" t="n">
-        <v>83.06</v>
+        <v>97.66</v>
       </c>
       <c r="M12" t="n">
-        <v>64.95</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>59.49</v>
+        <v>58.64</v>
       </c>
       <c r="O12" t="n">
-        <v>57.96</v>
+        <v>58.09</v>
       </c>
       <c r="P12" t="n">
-        <v>4849.02</v>
+        <v>11123.09</v>
       </c>
       <c r="Q12" t="n">
-        <v>3553.49</v>
+        <v>10417.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.36</v>
+        <v>1.07</v>
       </c>
       <c r="S12" t="n">
-        <v>337.02</v>
+        <v>108.21</v>
       </c>
       <c r="T12" t="n">
-        <v>359.71</v>
+        <v>117.85</v>
       </c>
       <c r="U12" t="n">
-        <v>331.13</v>
+        <v>107.77</v>
       </c>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
@@ -1338,69 +1338,69 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>988</v>
+        <v>603986</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>华工科技</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>114.93</v>
+        <v>250.49</v>
       </c>
       <c r="D13" t="n">
-        <v>4.09</v>
+        <v>-2.14</v>
       </c>
       <c r="E13" t="n">
-        <v>106.68</v>
+        <v>250.44</v>
       </c>
       <c r="F13" t="n">
-        <v>106.35</v>
+        <v>252.18</v>
       </c>
       <c r="G13" t="n">
-        <v>111.52</v>
+        <v>270.38</v>
       </c>
       <c r="H13" t="n">
-        <v>1.885</v>
+        <v>-10.086</v>
       </c>
       <c r="I13" t="n">
-        <v>2.961</v>
+        <v>-8.201000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>56.01</v>
+        <v>43.21</v>
       </c>
       <c r="K13" t="n">
-        <v>35.19</v>
+        <v>32.65</v>
       </c>
       <c r="L13" t="n">
-        <v>97.66</v>
+        <v>64.33</v>
       </c>
       <c r="M13" t="n">
-        <v>66.51000000000001</v>
+        <v>40.79</v>
       </c>
       <c r="N13" t="n">
-        <v>58.64</v>
+        <v>41.04</v>
       </c>
       <c r="O13" t="n">
-        <v>58.09</v>
+        <v>44.88</v>
       </c>
       <c r="P13" t="n">
-        <v>11123.09</v>
+        <v>4446.83</v>
       </c>
       <c r="Q13" t="n">
-        <v>10417.87</v>
+        <v>3358.48</v>
       </c>
       <c r="R13" t="n">
-        <v>1.07</v>
+        <v>1.32</v>
       </c>
       <c r="S13" t="n">
-        <v>108.21</v>
+        <v>250</v>
       </c>
       <c r="T13" t="n">
-        <v>117.85</v>
+        <v>253.49</v>
       </c>
       <c r="U13" t="n">
-        <v>107.77</v>
+        <v>243.9</v>
       </c>
       <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
@@ -1411,69 +1411,69 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>603986</v>
+        <v>300042</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>朗科科技</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>250.49</v>
+        <v>48.1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2.14</v>
+        <v>3.62</v>
       </c>
       <c r="E14" t="n">
-        <v>250.44</v>
+        <v>44.06</v>
       </c>
       <c r="F14" t="n">
-        <v>252.18</v>
+        <v>43.92</v>
       </c>
       <c r="G14" t="n">
-        <v>270.38</v>
+        <v>46.26</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.086</v>
+        <v>1.461</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.201000000000001</v>
+        <v>1.988</v>
       </c>
       <c r="J14" t="n">
-        <v>43.21</v>
+        <v>57.08</v>
       </c>
       <c r="K14" t="n">
-        <v>32.65</v>
+        <v>34.14</v>
       </c>
       <c r="L14" t="n">
-        <v>64.33</v>
+        <v>102.94</v>
       </c>
       <c r="M14" t="n">
-        <v>40.79</v>
+        <v>66.7</v>
       </c>
       <c r="N14" t="n">
-        <v>41.04</v>
+        <v>59.61</v>
       </c>
       <c r="O14" t="n">
-        <v>44.88</v>
+        <v>59.12</v>
       </c>
       <c r="P14" t="n">
-        <v>4446.83</v>
+        <v>4004.56</v>
       </c>
       <c r="Q14" t="n">
-        <v>3358.48</v>
+        <v>3194.13</v>
       </c>
       <c r="R14" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="S14" t="n">
-        <v>250</v>
+        <v>44.94</v>
       </c>
       <c r="T14" t="n">
-        <v>253.49</v>
+        <v>48.42</v>
       </c>
       <c r="U14" t="n">
-        <v>243.9</v>
+        <v>44.94</v>
       </c>
       <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
@@ -1484,69 +1484,69 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>688525</v>
+        <v>300302</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>同有科技</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>227.52</v>
+        <v>21.88</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9399999999999999</v>
+        <v>2.43</v>
       </c>
       <c r="E15" t="n">
-        <v>219.15</v>
+        <v>20.21</v>
       </c>
       <c r="F15" t="n">
-        <v>223.27</v>
+        <v>20.43</v>
       </c>
       <c r="G15" t="n">
-        <v>228.44</v>
+        <v>21.43</v>
       </c>
       <c r="H15" t="n">
-        <v>7.069</v>
+        <v>0.057</v>
       </c>
       <c r="I15" t="n">
-        <v>10.344</v>
+        <v>0.188</v>
       </c>
       <c r="J15" t="n">
-        <v>36.59</v>
+        <v>50.24</v>
       </c>
       <c r="K15" t="n">
-        <v>29.36</v>
+        <v>29.95</v>
       </c>
       <c r="L15" t="n">
-        <v>51.06</v>
+        <v>90.83</v>
       </c>
       <c r="M15" t="n">
-        <v>55.45</v>
+        <v>62.52</v>
       </c>
       <c r="N15" t="n">
-        <v>54.86</v>
+        <v>55.85</v>
       </c>
       <c r="O15" t="n">
-        <v>57</v>
+        <v>54.19</v>
       </c>
       <c r="P15" t="n">
-        <v>3243.78</v>
+        <v>4609.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>3858.28</v>
+        <v>4533.7</v>
       </c>
       <c r="R15" t="n">
-        <v>0.84</v>
+        <v>1.02</v>
       </c>
       <c r="S15" t="n">
-        <v>224</v>
+        <v>21.02</v>
       </c>
       <c r="T15" t="n">
-        <v>231.18</v>
+        <v>22.42</v>
       </c>
       <c r="U15" t="n">
-        <v>220.42</v>
+        <v>20.95</v>
       </c>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
@@ -1557,69 +1557,69 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>300042</v>
+        <v>20</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>朗科科技</t>
+          <t>深华发A</t>
         </is>
       </c>
       <c r="C16" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E16" t="n">
+        <v>15.34</v>
+      </c>
+      <c r="F16" t="n">
+        <v>15.91</v>
+      </c>
+      <c r="G16" t="n">
+        <v>17.15</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.151</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="J16" t="n">
+        <v>22.63</v>
+      </c>
+      <c r="K16" t="n">
+        <v>16.53</v>
+      </c>
+      <c r="L16" t="n">
+        <v>34.83</v>
+      </c>
+      <c r="M16" t="n">
+        <v>40.49</v>
+      </c>
+      <c r="N16" t="n">
+        <v>44.81</v>
+      </c>
+      <c r="O16" t="n">
         <v>48.1</v>
       </c>
-      <c r="D16" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="E16" t="n">
-        <v>44.06</v>
-      </c>
-      <c r="F16" t="n">
-        <v>43.92</v>
-      </c>
-      <c r="G16" t="n">
-        <v>46.26</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.461</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.988</v>
-      </c>
-      <c r="J16" t="n">
-        <v>57.08</v>
-      </c>
-      <c r="K16" t="n">
-        <v>34.14</v>
-      </c>
-      <c r="L16" t="n">
-        <v>102.94</v>
-      </c>
-      <c r="M16" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="N16" t="n">
-        <v>59.61</v>
-      </c>
-      <c r="O16" t="n">
-        <v>59.12</v>
-      </c>
       <c r="P16" t="n">
-        <v>4004.56</v>
+        <v>888.86</v>
       </c>
       <c r="Q16" t="n">
-        <v>3194.13</v>
+        <v>1405.63</v>
       </c>
       <c r="R16" t="n">
-        <v>1.25</v>
+        <v>0.63</v>
       </c>
       <c r="S16" t="n">
-        <v>44.94</v>
+        <v>15.5</v>
       </c>
       <c r="T16" t="n">
-        <v>48.42</v>
+        <v>15.79</v>
       </c>
       <c r="U16" t="n">
-        <v>44.94</v>
+        <v>15.37</v>
       </c>
       <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
@@ -1630,69 +1630,69 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>300302</v>
+        <v>603881</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>同有科技</t>
+          <t>数据港</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>21.88</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>2.43</v>
+        <v>-0.64</v>
       </c>
       <c r="E17" t="n">
-        <v>20.21</v>
+        <v>37.41</v>
       </c>
       <c r="F17" t="n">
-        <v>20.43</v>
+        <v>37.71</v>
       </c>
       <c r="G17" t="n">
-        <v>21.43</v>
+        <v>37.34</v>
       </c>
       <c r="H17" t="n">
-        <v>0.057</v>
+        <v>0.107</v>
       </c>
       <c r="I17" t="n">
-        <v>0.188</v>
+        <v>-0.012</v>
       </c>
       <c r="J17" t="n">
-        <v>50.24</v>
+        <v>63.21</v>
       </c>
       <c r="K17" t="n">
-        <v>29.95</v>
+        <v>53.63</v>
       </c>
       <c r="L17" t="n">
-        <v>90.83</v>
+        <v>82.38</v>
       </c>
       <c r="M17" t="n">
-        <v>62.52</v>
+        <v>60.34</v>
       </c>
       <c r="N17" t="n">
-        <v>55.85</v>
+        <v>55.01</v>
       </c>
       <c r="O17" t="n">
-        <v>54.19</v>
+        <v>53.37</v>
       </c>
       <c r="P17" t="n">
-        <v>4609.88</v>
+        <v>8354.639999999999</v>
       </c>
       <c r="Q17" t="n">
-        <v>4533.7</v>
+        <v>6144.36</v>
       </c>
       <c r="R17" t="n">
-        <v>1.02</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>21.02</v>
+        <v>38.98</v>
       </c>
       <c r="T17" t="n">
-        <v>22.42</v>
+        <v>39.69</v>
       </c>
       <c r="U17" t="n">
-        <v>20.95</v>
+        <v>38.61</v>
       </c>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
@@ -1703,69 +1703,69 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>20</v>
+        <v>300017</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>深华发A</t>
+          <t>网宿科技</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>15.58</v>
+        <v>17.95</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.19</v>
+        <v>-2.55</v>
       </c>
       <c r="E18" t="n">
-        <v>15.34</v>
+        <v>17.1</v>
       </c>
       <c r="F18" t="n">
-        <v>15.91</v>
+        <v>17.26</v>
       </c>
       <c r="G18" t="n">
-        <v>17.15</v>
+        <v>17.5</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.151</v>
+        <v>-0.124</v>
       </c>
       <c r="I18" t="n">
-        <v>0.226</v>
+        <v>-0.102</v>
       </c>
       <c r="J18" t="n">
-        <v>22.63</v>
+        <v>54.93</v>
       </c>
       <c r="K18" t="n">
-        <v>16.53</v>
+        <v>38.41</v>
       </c>
       <c r="L18" t="n">
-        <v>34.83</v>
+        <v>87.95</v>
       </c>
       <c r="M18" t="n">
-        <v>40.49</v>
+        <v>56.72</v>
       </c>
       <c r="N18" t="n">
-        <v>44.81</v>
+        <v>52.3</v>
       </c>
       <c r="O18" t="n">
-        <v>48.1</v>
+        <v>53.06</v>
       </c>
       <c r="P18" t="n">
-        <v>888.86</v>
+        <v>19410.83</v>
       </c>
       <c r="Q18" t="n">
-        <v>1405.63</v>
+        <v>22636.3</v>
       </c>
       <c r="R18" t="n">
-        <v>0.63</v>
+        <v>0.86</v>
       </c>
       <c r="S18" t="n">
-        <v>15.5</v>
+        <v>17.7</v>
       </c>
       <c r="T18" t="n">
-        <v>15.79</v>
+        <v>18.08</v>
       </c>
       <c r="U18" t="n">
-        <v>15.37</v>
+        <v>17.62</v>
       </c>
       <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
@@ -1776,69 +1776,69 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>603881</v>
+        <v>300418</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>数据港</t>
+          <t>昆仑万维</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>39</v>
+        <v>50.46</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.64</v>
+        <v>-3.7</v>
       </c>
       <c r="E19" t="n">
-        <v>37.41</v>
+        <v>48.86</v>
       </c>
       <c r="F19" t="n">
-        <v>37.71</v>
+        <v>49.63</v>
       </c>
       <c r="G19" t="n">
-        <v>37.34</v>
+        <v>50.34</v>
       </c>
       <c r="H19" t="n">
-        <v>0.107</v>
+        <v>-1.201</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.012</v>
+        <v>-1.333</v>
       </c>
       <c r="J19" t="n">
-        <v>63.21</v>
+        <v>52.18</v>
       </c>
       <c r="K19" t="n">
-        <v>53.63</v>
+        <v>38.27</v>
       </c>
       <c r="L19" t="n">
-        <v>82.38</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>60.34</v>
+        <v>52.51</v>
       </c>
       <c r="N19" t="n">
-        <v>55.01</v>
+        <v>48.87</v>
       </c>
       <c r="O19" t="n">
-        <v>53.37</v>
+        <v>48.8</v>
       </c>
       <c r="P19" t="n">
-        <v>8354.639999999999</v>
+        <v>5129.19</v>
       </c>
       <c r="Q19" t="n">
-        <v>6144.36</v>
+        <v>6204.26</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>0.83</v>
       </c>
       <c r="S19" t="n">
-        <v>38.98</v>
+        <v>50.85</v>
       </c>
       <c r="T19" t="n">
-        <v>39.69</v>
+        <v>51.5</v>
       </c>
       <c r="U19" t="n">
-        <v>38.61</v>
+        <v>50.32</v>
       </c>
       <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
@@ -1849,69 +1849,69 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>300017</v>
+        <v>2230</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>网宿科技</t>
+          <t>科大讯飞</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>17.95</v>
+        <v>47.21</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.55</v>
+        <v>-1.46</v>
       </c>
       <c r="E20" t="n">
-        <v>17.1</v>
+        <v>46.46</v>
       </c>
       <c r="F20" t="n">
-        <v>17.26</v>
+        <v>46.52</v>
       </c>
       <c r="G20" t="n">
-        <v>17.5</v>
+        <v>48.24</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.124</v>
+        <v>-1.844</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.102</v>
+        <v>-2.046</v>
       </c>
       <c r="J20" t="n">
-        <v>54.93</v>
+        <v>52.57</v>
       </c>
       <c r="K20" t="n">
-        <v>38.41</v>
+        <v>34.28</v>
       </c>
       <c r="L20" t="n">
-        <v>87.95</v>
+        <v>89.14</v>
       </c>
       <c r="M20" t="n">
-        <v>56.72</v>
+        <v>50.97</v>
       </c>
       <c r="N20" t="n">
-        <v>52.3</v>
+        <v>41.63</v>
       </c>
       <c r="O20" t="n">
-        <v>53.06</v>
+        <v>40.64</v>
       </c>
       <c r="P20" t="n">
-        <v>19410.83</v>
+        <v>3024.52</v>
       </c>
       <c r="Q20" t="n">
-        <v>22636.3</v>
+        <v>3039.33</v>
       </c>
       <c r="R20" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="S20" t="n">
-        <v>17.7</v>
+        <v>47.26</v>
       </c>
       <c r="T20" t="n">
-        <v>18.08</v>
+        <v>47.41</v>
       </c>
       <c r="U20" t="n">
-        <v>17.62</v>
+        <v>46.8</v>
       </c>
       <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
@@ -1922,69 +1922,69 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>300418</v>
+        <v>300058</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>昆仑万维</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>50.46</v>
+        <v>16.66</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.7</v>
+        <v>2.15</v>
       </c>
       <c r="E21" t="n">
-        <v>48.86</v>
+        <v>14.76</v>
       </c>
       <c r="F21" t="n">
-        <v>49.63</v>
+        <v>14.59</v>
       </c>
       <c r="G21" t="n">
-        <v>50.34</v>
+        <v>14.7</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.201</v>
+        <v>-0.433</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.333</v>
+        <v>-0.747</v>
       </c>
       <c r="J21" t="n">
-        <v>52.18</v>
+        <v>63.33</v>
       </c>
       <c r="K21" t="n">
-        <v>38.27</v>
+        <v>45.72</v>
       </c>
       <c r="L21" t="n">
-        <v>79.98999999999999</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>52.51</v>
+        <v>74.64</v>
       </c>
       <c r="N21" t="n">
-        <v>48.87</v>
+        <v>60.49</v>
       </c>
       <c r="O21" t="n">
-        <v>48.8</v>
+        <v>53.68</v>
       </c>
       <c r="P21" t="n">
-        <v>5129.19</v>
+        <v>86507.42999999999</v>
       </c>
       <c r="Q21" t="n">
-        <v>6204.26</v>
+        <v>29599.46</v>
       </c>
       <c r="R21" t="n">
-        <v>0.83</v>
+        <v>2.92</v>
       </c>
       <c r="S21" t="n">
-        <v>50.85</v>
+        <v>16.4</v>
       </c>
       <c r="T21" t="n">
-        <v>51.5</v>
+        <v>16.95</v>
       </c>
       <c r="U21" t="n">
-        <v>50.32</v>
+        <v>16.14</v>
       </c>
       <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
@@ -1995,69 +1995,69 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2230</v>
+        <v>300496</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>科大讯飞</t>
+          <t>中科创达</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>47.21</v>
+        <v>59.68</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.46</v>
+        <v>-2.63</v>
       </c>
       <c r="E22" t="n">
-        <v>46.46</v>
+        <v>58.43</v>
       </c>
       <c r="F22" t="n">
-        <v>46.52</v>
+        <v>58.73</v>
       </c>
       <c r="G22" t="n">
-        <v>48.24</v>
+        <v>61.65</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.844</v>
+        <v>-2.809</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.046</v>
+        <v>-3.023</v>
       </c>
       <c r="J22" t="n">
-        <v>52.57</v>
+        <v>47.5</v>
       </c>
       <c r="K22" t="n">
-        <v>34.28</v>
+        <v>29.48</v>
       </c>
       <c r="L22" t="n">
-        <v>89.14</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>50.97</v>
+        <v>49.87</v>
       </c>
       <c r="N22" t="n">
-        <v>41.63</v>
+        <v>41.94</v>
       </c>
       <c r="O22" t="n">
-        <v>40.64</v>
+        <v>40.74</v>
       </c>
       <c r="P22" t="n">
-        <v>3024.52</v>
+        <v>943.6799999999999</v>
       </c>
       <c r="Q22" t="n">
-        <v>3039.33</v>
+        <v>1049.34</v>
       </c>
       <c r="R22" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="S22" t="n">
-        <v>47.26</v>
+        <v>60.13</v>
       </c>
       <c r="T22" t="n">
-        <v>47.41</v>
+        <v>60.39</v>
       </c>
       <c r="U22" t="n">
-        <v>46.8</v>
+        <v>59.58</v>
       </c>
       <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
@@ -2068,69 +2068,69 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>300058</v>
+        <v>547</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>蓝色光标</t>
+          <t>航天发展</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>16.66</v>
+        <v>26.78</v>
       </c>
       <c r="D23" t="n">
-        <v>2.15</v>
+        <v>-2.97</v>
       </c>
       <c r="E23" t="n">
-        <v>14.76</v>
+        <v>26.62</v>
       </c>
       <c r="F23" t="n">
-        <v>14.59</v>
+        <v>27.36</v>
       </c>
       <c r="G23" t="n">
-        <v>14.7</v>
+        <v>28.43</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.433</v>
+        <v>-0.909</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.747</v>
+        <v>-0.743</v>
       </c>
       <c r="J23" t="n">
-        <v>63.33</v>
+        <v>32.52</v>
       </c>
       <c r="K23" t="n">
-        <v>45.72</v>
+        <v>34.47</v>
       </c>
       <c r="L23" t="n">
-        <v>98.54000000000001</v>
+        <v>28.62</v>
       </c>
       <c r="M23" t="n">
-        <v>74.64</v>
+        <v>43.22</v>
       </c>
       <c r="N23" t="n">
-        <v>60.49</v>
+        <v>43.06</v>
       </c>
       <c r="O23" t="n">
-        <v>53.68</v>
+        <v>46.13</v>
       </c>
       <c r="P23" t="n">
-        <v>86507.42999999999</v>
+        <v>13363.43</v>
       </c>
       <c r="Q23" t="n">
-        <v>29599.46</v>
+        <v>18934.93</v>
       </c>
       <c r="R23" t="n">
-        <v>2.92</v>
+        <v>0.71</v>
       </c>
       <c r="S23" t="n">
-        <v>16.4</v>
+        <v>27.18</v>
       </c>
       <c r="T23" t="n">
-        <v>16.95</v>
+        <v>27.5</v>
       </c>
       <c r="U23" t="n">
-        <v>16.14</v>
+        <v>26.65</v>
       </c>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
@@ -2141,69 +2141,69 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>300496</v>
+        <v>2202</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>中科创达</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>59.68</v>
+        <v>23.84</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.63</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>58.43</v>
+        <v>23.76</v>
       </c>
       <c r="F24" t="n">
-        <v>58.73</v>
+        <v>25.38</v>
       </c>
       <c r="G24" t="n">
-        <v>61.65</v>
+        <v>27.47</v>
       </c>
       <c r="H24" t="n">
-        <v>-2.809</v>
+        <v>-1.107</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.023</v>
+        <v>-0.509</v>
       </c>
       <c r="J24" t="n">
-        <v>47.5</v>
+        <v>14.09</v>
       </c>
       <c r="K24" t="n">
-        <v>29.48</v>
+        <v>12.53</v>
       </c>
       <c r="L24" t="n">
-        <v>83.54000000000001</v>
+        <v>17.2</v>
       </c>
       <c r="M24" t="n">
-        <v>49.87</v>
+        <v>31.03</v>
       </c>
       <c r="N24" t="n">
-        <v>41.94</v>
+        <v>35.83</v>
       </c>
       <c r="O24" t="n">
-        <v>40.74</v>
+        <v>43.71</v>
       </c>
       <c r="P24" t="n">
-        <v>943.6799999999999</v>
+        <v>21323.37</v>
       </c>
       <c r="Q24" t="n">
-        <v>1049.34</v>
+        <v>27669.12</v>
       </c>
       <c r="R24" t="n">
-        <v>0.9</v>
+        <v>0.77</v>
       </c>
       <c r="S24" t="n">
-        <v>60.13</v>
+        <v>23.42</v>
       </c>
       <c r="T24" t="n">
-        <v>60.39</v>
+        <v>24.2</v>
       </c>
       <c r="U24" t="n">
-        <v>59.58</v>
+        <v>23.01</v>
       </c>
       <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
@@ -2214,69 +2214,69 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>547</v>
+        <v>301128</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>航天发展</t>
+          <t>强瑞技术</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>26.78</v>
+        <v>163.33</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.97</v>
+        <v>2.57</v>
       </c>
       <c r="E25" t="n">
-        <v>26.62</v>
+        <v>155.05</v>
       </c>
       <c r="F25" t="n">
-        <v>27.36</v>
+        <v>149.1</v>
       </c>
       <c r="G25" t="n">
-        <v>28.43</v>
+        <v>136.17</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.909</v>
+        <v>12.371</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.743</v>
+        <v>10.431</v>
       </c>
       <c r="J25" t="n">
-        <v>32.52</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>34.47</v>
+        <v>77.36</v>
       </c>
       <c r="L25" t="n">
-        <v>28.62</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>43.22</v>
+        <v>73.98</v>
       </c>
       <c r="N25" t="n">
-        <v>43.06</v>
+        <v>71.44</v>
       </c>
       <c r="O25" t="n">
-        <v>46.13</v>
+        <v>68.15000000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>13363.43</v>
+        <v>713.74</v>
       </c>
       <c r="Q25" t="n">
-        <v>18934.93</v>
+        <v>916.46</v>
       </c>
       <c r="R25" t="n">
-        <v>0.71</v>
+        <v>0.78</v>
       </c>
       <c r="S25" t="n">
-        <v>27.18</v>
+        <v>158.91</v>
       </c>
       <c r="T25" t="n">
-        <v>27.5</v>
+        <v>168.2</v>
       </c>
       <c r="U25" t="n">
-        <v>26.65</v>
+        <v>154.61</v>
       </c>
       <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
@@ -2287,69 +2287,69 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2202</v>
+        <v>601899</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>金风科技</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>23.84</v>
+        <v>33.9</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>-2.08</v>
       </c>
       <c r="E26" t="n">
-        <v>23.76</v>
+        <v>33.39</v>
       </c>
       <c r="F26" t="n">
-        <v>25.38</v>
+        <v>33.12</v>
       </c>
       <c r="G26" t="n">
-        <v>27.47</v>
+        <v>33.41</v>
       </c>
       <c r="H26" t="n">
-        <v>-1.107</v>
+        <v>-0.84</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.509</v>
+        <v>-1.128</v>
       </c>
       <c r="J26" t="n">
-        <v>14.09</v>
+        <v>68.75</v>
       </c>
       <c r="K26" t="n">
-        <v>12.53</v>
+        <v>62.31</v>
       </c>
       <c r="L26" t="n">
-        <v>17.2</v>
+        <v>81.63</v>
       </c>
       <c r="M26" t="n">
-        <v>31.03</v>
+        <v>55.04</v>
       </c>
       <c r="N26" t="n">
-        <v>35.83</v>
+        <v>48.85</v>
       </c>
       <c r="O26" t="n">
-        <v>43.71</v>
+        <v>47.22</v>
       </c>
       <c r="P26" t="n">
-        <v>21323.37</v>
+        <v>22065.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>27669.12</v>
+        <v>30413.65</v>
       </c>
       <c r="R26" t="n">
-        <v>0.77</v>
+        <v>0.73</v>
       </c>
       <c r="S26" t="n">
-        <v>23.42</v>
+        <v>33.99</v>
       </c>
       <c r="T26" t="n">
-        <v>24.2</v>
+        <v>34.19</v>
       </c>
       <c r="U26" t="n">
-        <v>23.01</v>
+        <v>33.74</v>
       </c>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
@@ -2360,69 +2360,69 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>301128</v>
+        <v>600219</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>强瑞技术</t>
+          <t>南山铝业</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>163.33</v>
+        <v>6.32</v>
       </c>
       <c r="D27" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
-        <v>155.05</v>
+        <v>6.17</v>
       </c>
       <c r="F27" t="n">
-        <v>149.1</v>
+        <v>6.15</v>
       </c>
       <c r="G27" t="n">
-        <v>136.17</v>
+        <v>6.34</v>
       </c>
       <c r="H27" t="n">
-        <v>12.371</v>
+        <v>-0.179</v>
       </c>
       <c r="I27" t="n">
-        <v>10.431</v>
+        <v>-0.198</v>
       </c>
       <c r="J27" t="n">
-        <v>79.29000000000001</v>
+        <v>56.28</v>
       </c>
       <c r="K27" t="n">
-        <v>77.36</v>
+        <v>47.63</v>
       </c>
       <c r="L27" t="n">
-        <v>83.15000000000001</v>
+        <v>73.58</v>
       </c>
       <c r="M27" t="n">
-        <v>73.98</v>
+        <v>55.88</v>
       </c>
       <c r="N27" t="n">
-        <v>71.44</v>
+        <v>48.34</v>
       </c>
       <c r="O27" t="n">
-        <v>68.15000000000001</v>
+        <v>48.67</v>
       </c>
       <c r="P27" t="n">
-        <v>713.74</v>
+        <v>20041.74</v>
       </c>
       <c r="Q27" t="n">
-        <v>916.46</v>
+        <v>27438.2</v>
       </c>
       <c r="R27" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="S27" t="n">
-        <v>158.91</v>
+        <v>6.25</v>
       </c>
       <c r="T27" t="n">
-        <v>168.2</v>
+        <v>6.39</v>
       </c>
       <c r="U27" t="n">
-        <v>154.61</v>
+        <v>6.18</v>
       </c>
       <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
@@ -2433,69 +2433,69 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>601899</v>
+        <v>601939</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>建设银行</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>33.9</v>
+        <v>9.27</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.08</v>
+        <v>-0.32</v>
       </c>
       <c r="E28" t="n">
-        <v>33.39</v>
+        <v>9.35</v>
       </c>
       <c r="F28" t="n">
-        <v>33.12</v>
+        <v>9.42</v>
       </c>
       <c r="G28" t="n">
-        <v>33.41</v>
+        <v>9.34</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.84</v>
+        <v>0.094</v>
       </c>
       <c r="I28" t="n">
-        <v>-1.128</v>
+        <v>0.126</v>
       </c>
       <c r="J28" t="n">
-        <v>68.75</v>
+        <v>38.64</v>
       </c>
       <c r="K28" t="n">
-        <v>62.31</v>
+        <v>52.98</v>
       </c>
       <c r="L28" t="n">
-        <v>81.63</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>55.04</v>
+        <v>42.49</v>
       </c>
       <c r="N28" t="n">
-        <v>48.85</v>
+        <v>49.73</v>
       </c>
       <c r="O28" t="n">
-        <v>47.22</v>
+        <v>52.87</v>
       </c>
       <c r="P28" t="n">
-        <v>22065.9</v>
+        <v>5395.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>30413.65</v>
+        <v>9613.120000000001</v>
       </c>
       <c r="R28" t="n">
-        <v>0.73</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.99</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="T28" t="n">
-        <v>34.19</v>
+        <v>9.31</v>
       </c>
       <c r="U28" t="n">
-        <v>33.74</v>
+        <v>9.18</v>
       </c>
       <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
@@ -2506,69 +2506,69 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>600219</v>
+        <v>600048</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>南山铝业</t>
+          <t>保利发展</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>6.32</v>
+        <v>5.57</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
+        <v>-2.28</v>
       </c>
       <c r="E29" t="n">
-        <v>6.17</v>
+        <v>5.6</v>
       </c>
       <c r="F29" t="n">
-        <v>6.15</v>
+        <v>5.73</v>
       </c>
       <c r="G29" t="n">
-        <v>6.34</v>
+        <v>5.99</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.179</v>
+        <v>-0.25</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.198</v>
+        <v>-0.223</v>
       </c>
       <c r="J29" t="n">
-        <v>56.28</v>
+        <v>19.48</v>
       </c>
       <c r="K29" t="n">
-        <v>47.63</v>
+        <v>14.6</v>
       </c>
       <c r="L29" t="n">
-        <v>73.58</v>
+        <v>29.25</v>
       </c>
       <c r="M29" t="n">
-        <v>55.88</v>
+        <v>32.86</v>
       </c>
       <c r="N29" t="n">
-        <v>48.34</v>
+        <v>30.82</v>
       </c>
       <c r="O29" t="n">
-        <v>48.67</v>
+        <v>34.84</v>
       </c>
       <c r="P29" t="n">
-        <v>20041.74</v>
+        <v>10884.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>27438.2</v>
+        <v>10996.33</v>
       </c>
       <c r="R29" t="n">
-        <v>0.73</v>
+        <v>0.99</v>
       </c>
       <c r="S29" t="n">
-        <v>6.25</v>
+        <v>5.65</v>
       </c>
       <c r="T29" t="n">
-        <v>6.39</v>
+        <v>5.66</v>
       </c>
       <c r="U29" t="n">
-        <v>6.18</v>
+        <v>5.53</v>
       </c>
       <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
@@ -2579,69 +2579,69 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>601939</v>
+        <v>600941</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>建设银行</t>
+          <t>中国移动</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>9.27</v>
+        <v>93.64</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.32</v>
+        <v>-0.37</v>
       </c>
       <c r="E30" t="n">
-        <v>9.35</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>9.42</v>
+        <v>93.56</v>
       </c>
       <c r="G30" t="n">
-        <v>9.34</v>
+        <v>94.95</v>
       </c>
       <c r="H30" t="n">
-        <v>0.094</v>
+        <v>-0.642</v>
       </c>
       <c r="I30" t="n">
-        <v>0.126</v>
+        <v>-0.5620000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>38.64</v>
+        <v>52.95</v>
       </c>
       <c r="K30" t="n">
-        <v>52.98</v>
+        <v>40.86</v>
       </c>
       <c r="L30" t="n">
-        <v>9.949999999999999</v>
+        <v>77.13</v>
       </c>
       <c r="M30" t="n">
-        <v>42.49</v>
+        <v>44.51</v>
       </c>
       <c r="N30" t="n">
-        <v>49.73</v>
+        <v>43.15</v>
       </c>
       <c r="O30" t="n">
-        <v>52.87</v>
+        <v>43.35</v>
       </c>
       <c r="P30" t="n">
-        <v>5395.21</v>
+        <v>528.35</v>
       </c>
       <c r="Q30" t="n">
-        <v>9613.120000000001</v>
+        <v>942.5599999999999</v>
       </c>
       <c r="R30" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="S30" t="n">
-        <v>9.289999999999999</v>
+        <v>93.75</v>
       </c>
       <c r="T30" t="n">
-        <v>9.31</v>
+        <v>93.78</v>
       </c>
       <c r="U30" t="n">
-        <v>9.18</v>
+        <v>93.36</v>
       </c>
       <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
@@ -2652,69 +2652,69 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>600048</v>
+        <v>2352</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>保利发展</t>
+          <t>顺丰控股</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.57</v>
+        <v>37.53</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.28</v>
+        <v>-1.11</v>
       </c>
       <c r="E31" t="n">
-        <v>5.6</v>
+        <v>37.8</v>
       </c>
       <c r="F31" t="n">
-        <v>5.73</v>
+        <v>37.57</v>
       </c>
       <c r="G31" t="n">
-        <v>5.99</v>
+        <v>37.21</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.25</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.223</v>
+        <v>-0.06</v>
       </c>
       <c r="J31" t="n">
-        <v>19.48</v>
+        <v>65.08</v>
       </c>
       <c r="K31" t="n">
-        <v>14.6</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>29.25</v>
+        <v>58.82</v>
       </c>
       <c r="M31" t="n">
-        <v>32.86</v>
+        <v>50.38</v>
       </c>
       <c r="N31" t="n">
-        <v>30.82</v>
+        <v>51.49</v>
       </c>
       <c r="O31" t="n">
-        <v>34.84</v>
+        <v>49.92</v>
       </c>
       <c r="P31" t="n">
-        <v>10884.1</v>
+        <v>1400.82</v>
       </c>
       <c r="Q31" t="n">
-        <v>10996.33</v>
+        <v>2306.95</v>
       </c>
       <c r="R31" t="n">
-        <v>0.99</v>
+        <v>0.61</v>
       </c>
       <c r="S31" t="n">
-        <v>5.65</v>
+        <v>37.8</v>
       </c>
       <c r="T31" t="n">
-        <v>5.66</v>
+        <v>37.94</v>
       </c>
       <c r="U31" t="n">
-        <v>5.53</v>
+        <v>37.47</v>
       </c>
       <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
@@ -2725,69 +2725,69 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>600941</v>
+        <v>603803</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>中国移动</t>
+          <t>瑞斯康达</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>93.64</v>
+        <v>14.34</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.37</v>
+        <v>2.43</v>
       </c>
       <c r="E32" t="n">
-        <v>93.45999999999999</v>
+        <v>13.59</v>
       </c>
       <c r="F32" t="n">
-        <v>93.56</v>
+        <v>13.58</v>
       </c>
       <c r="G32" t="n">
-        <v>94.95</v>
+        <v>13.64</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.642</v>
+        <v>0.599</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.5620000000000001</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>52.95</v>
+        <v>55.14</v>
       </c>
       <c r="K32" t="n">
-        <v>40.86</v>
+        <v>42.31</v>
       </c>
       <c r="L32" t="n">
-        <v>77.13</v>
+        <v>80.79000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>44.51</v>
+        <v>62.63</v>
       </c>
       <c r="N32" t="n">
-        <v>43.15</v>
+        <v>59.44</v>
       </c>
       <c r="O32" t="n">
-        <v>43.35</v>
+        <v>58.64</v>
       </c>
       <c r="P32" t="n">
-        <v>528.35</v>
+        <v>9157.450000000001</v>
       </c>
       <c r="Q32" t="n">
-        <v>942.5599999999999</v>
+        <v>9458.120000000001</v>
       </c>
       <c r="R32" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.97</v>
       </c>
       <c r="S32" t="n">
-        <v>93.75</v>
+        <v>13.8</v>
       </c>
       <c r="T32" t="n">
-        <v>93.78</v>
+        <v>14.5</v>
       </c>
       <c r="U32" t="n">
-        <v>93.36</v>
+        <v>13.46</v>
       </c>
       <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
@@ -2798,69 +2798,69 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2352</v>
+        <v>2624</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>顺丰控股</t>
+          <t>完美世界</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>37.53</v>
+        <v>20.06</v>
       </c>
       <c r="D33" t="n">
-        <v>-1.11</v>
+        <v>-0.79</v>
       </c>
       <c r="E33" t="n">
-        <v>37.8</v>
+        <v>19.73</v>
       </c>
       <c r="F33" t="n">
-        <v>37.57</v>
+        <v>18.98</v>
       </c>
       <c r="G33" t="n">
-        <v>37.21</v>
+        <v>18.8</v>
       </c>
       <c r="H33" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.055</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.06</v>
+        <v>-0.181</v>
       </c>
       <c r="J33" t="n">
-        <v>65.08</v>
+        <v>79.02</v>
       </c>
       <c r="K33" t="n">
-        <v>68.20999999999999</v>
+        <v>70.5</v>
       </c>
       <c r="L33" t="n">
-        <v>58.82</v>
+        <v>96.05</v>
       </c>
       <c r="M33" t="n">
-        <v>50.38</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>51.49</v>
+        <v>58.48</v>
       </c>
       <c r="O33" t="n">
-        <v>49.92</v>
+        <v>55.28</v>
       </c>
       <c r="P33" t="n">
-        <v>1400.82</v>
+        <v>5657.55</v>
       </c>
       <c r="Q33" t="n">
-        <v>2306.95</v>
+        <v>5379.73</v>
       </c>
       <c r="R33" t="n">
-        <v>0.61</v>
+        <v>1.05</v>
       </c>
       <c r="S33" t="n">
-        <v>37.8</v>
+        <v>20</v>
       </c>
       <c r="T33" t="n">
-        <v>37.94</v>
+        <v>20.25</v>
       </c>
       <c r="U33" t="n">
-        <v>37.47</v>
+        <v>19.71</v>
       </c>
       <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
@@ -2871,69 +2871,69 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>603803</v>
+        <v>2558</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>瑞斯康达</t>
+          <t>巨人网络</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>14.34</v>
+        <v>32.97</v>
       </c>
       <c r="D34" t="n">
-        <v>2.43</v>
+        <v>-4.66</v>
       </c>
       <c r="E34" t="n">
-        <v>13.59</v>
+        <v>33.54</v>
       </c>
       <c r="F34" t="n">
-        <v>13.58</v>
+        <v>32.93</v>
       </c>
       <c r="G34" t="n">
-        <v>13.64</v>
+        <v>33.27</v>
       </c>
       <c r="H34" t="n">
-        <v>0.599</v>
+        <v>-1.152</v>
       </c>
       <c r="I34" t="n">
-        <v>0.6919999999999999</v>
+        <v>-1.612</v>
       </c>
       <c r="J34" t="n">
-        <v>55.14</v>
+        <v>57.48</v>
       </c>
       <c r="K34" t="n">
-        <v>42.31</v>
+        <v>53.61</v>
       </c>
       <c r="L34" t="n">
-        <v>80.79000000000001</v>
+        <v>65.23</v>
       </c>
       <c r="M34" t="n">
-        <v>62.63</v>
+        <v>47.18</v>
       </c>
       <c r="N34" t="n">
-        <v>59.44</v>
+        <v>44.47</v>
       </c>
       <c r="O34" t="n">
-        <v>58.64</v>
+        <v>41.4</v>
       </c>
       <c r="P34" t="n">
-        <v>9157.450000000001</v>
+        <v>5564.55</v>
       </c>
       <c r="Q34" t="n">
-        <v>9458.120000000001</v>
+        <v>4114.4</v>
       </c>
       <c r="R34" t="n">
-        <v>0.97</v>
+        <v>1.35</v>
       </c>
       <c r="S34" t="n">
-        <v>13.8</v>
+        <v>33.9</v>
       </c>
       <c r="T34" t="n">
-        <v>14.5</v>
+        <v>33.93</v>
       </c>
       <c r="U34" t="n">
-        <v>13.46</v>
+        <v>32.5</v>
       </c>
       <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
@@ -2944,69 +2944,69 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2624</v>
+        <v>601088</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>完美世界</t>
+          <t>中国神华</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>20.06</v>
+        <v>46.79</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.79</v>
+        <v>0.06</v>
       </c>
       <c r="E35" t="n">
-        <v>19.73</v>
+        <v>47.45</v>
       </c>
       <c r="F35" t="n">
-        <v>18.98</v>
+        <v>47.36</v>
       </c>
       <c r="G35" t="n">
-        <v>18.8</v>
+        <v>47.99</v>
       </c>
       <c r="H35" t="n">
-        <v>0.055</v>
+        <v>0.525</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.181</v>
+        <v>0.864</v>
       </c>
       <c r="J35" t="n">
-        <v>79.02</v>
+        <v>42.97</v>
       </c>
       <c r="K35" t="n">
-        <v>70.5</v>
+        <v>42.88</v>
       </c>
       <c r="L35" t="n">
-        <v>96.05</v>
+        <v>43.16</v>
       </c>
       <c r="M35" t="n">
-        <v>67.48999999999999</v>
+        <v>40.67</v>
       </c>
       <c r="N35" t="n">
-        <v>58.48</v>
+        <v>48.24</v>
       </c>
       <c r="O35" t="n">
-        <v>55.28</v>
+        <v>53.53</v>
       </c>
       <c r="P35" t="n">
-        <v>5657.55</v>
+        <v>2224.18</v>
       </c>
       <c r="Q35" t="n">
-        <v>5379.73</v>
+        <v>3937.51</v>
       </c>
       <c r="R35" t="n">
-        <v>1.05</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="S35" t="n">
-        <v>20</v>
+        <v>46.8</v>
       </c>
       <c r="T35" t="n">
-        <v>20.25</v>
+        <v>47.3</v>
       </c>
       <c r="U35" t="n">
-        <v>19.71</v>
+        <v>46.58</v>
       </c>
       <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
@@ -3017,69 +3017,69 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2558</v>
+        <v>600963</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>巨人网络</t>
+          <t>岳阳林纸</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>32.97</v>
+        <v>4.8</v>
       </c>
       <c r="D36" t="n">
-        <v>-4.66</v>
+        <v>-1.44</v>
       </c>
       <c r="E36" t="n">
-        <v>33.54</v>
+        <v>4.76</v>
       </c>
       <c r="F36" t="n">
-        <v>32.93</v>
+        <v>4.78</v>
       </c>
       <c r="G36" t="n">
-        <v>33.27</v>
+        <v>4.96</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.152</v>
+        <v>-0.216</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.612</v>
+        <v>-0.222</v>
       </c>
       <c r="J36" t="n">
-        <v>57.48</v>
+        <v>53.04</v>
       </c>
       <c r="K36" t="n">
-        <v>53.61</v>
+        <v>45.1</v>
       </c>
       <c r="L36" t="n">
-        <v>65.23</v>
+        <v>68.92</v>
       </c>
       <c r="M36" t="n">
-        <v>47.18</v>
+        <v>46.6</v>
       </c>
       <c r="N36" t="n">
-        <v>44.47</v>
+        <v>41.23</v>
       </c>
       <c r="O36" t="n">
-        <v>41.4</v>
+        <v>43.87</v>
       </c>
       <c r="P36" t="n">
-        <v>5564.55</v>
+        <v>2181.66</v>
       </c>
       <c r="Q36" t="n">
-        <v>4114.4</v>
+        <v>3704.25</v>
       </c>
       <c r="R36" t="n">
-        <v>1.35</v>
+        <v>0.59</v>
       </c>
       <c r="S36" t="n">
-        <v>33.9</v>
+        <v>4.86</v>
       </c>
       <c r="T36" t="n">
-        <v>33.93</v>
+        <v>4.86</v>
       </c>
       <c r="U36" t="n">
-        <v>32.5</v>
+        <v>4.77</v>
       </c>
       <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
@@ -3090,69 +3090,69 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>601088</v>
+        <v>601877</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>中国神华</t>
+          <t>正泰电器</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>46.79</v>
+        <v>32.75</v>
       </c>
       <c r="D37" t="n">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="E37" t="n">
-        <v>47.45</v>
+        <v>31.97</v>
       </c>
       <c r="F37" t="n">
-        <v>47.36</v>
+        <v>32.71</v>
       </c>
       <c r="G37" t="n">
-        <v>47.99</v>
+        <v>34.34</v>
       </c>
       <c r="H37" t="n">
-        <v>0.525</v>
+        <v>-0.524</v>
       </c>
       <c r="I37" t="n">
-        <v>0.864</v>
+        <v>-0.134</v>
       </c>
       <c r="J37" t="n">
-        <v>42.97</v>
+        <v>29.39</v>
       </c>
       <c r="K37" t="n">
-        <v>42.88</v>
+        <v>20.08</v>
       </c>
       <c r="L37" t="n">
-        <v>43.16</v>
+        <v>48.01</v>
       </c>
       <c r="M37" t="n">
-        <v>40.67</v>
+        <v>46.98</v>
       </c>
       <c r="N37" t="n">
-        <v>48.24</v>
+        <v>45.06</v>
       </c>
       <c r="O37" t="n">
-        <v>53.53</v>
+        <v>48.96</v>
       </c>
       <c r="P37" t="n">
-        <v>2224.18</v>
+        <v>2487.67</v>
       </c>
       <c r="Q37" t="n">
-        <v>3937.51</v>
+        <v>4399.3</v>
       </c>
       <c r="R37" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.57</v>
       </c>
       <c r="S37" t="n">
-        <v>46.8</v>
+        <v>32.34</v>
       </c>
       <c r="T37" t="n">
-        <v>47.3</v>
+        <v>33.06</v>
       </c>
       <c r="U37" t="n">
-        <v>46.58</v>
+        <v>32.21</v>
       </c>
       <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
@@ -3163,69 +3163,69 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>600963</v>
+        <v>2049</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>岳阳林纸</t>
+          <t>紫光国微</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.8</v>
+        <v>68.48</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.44</v>
+        <v>-0.77</v>
       </c>
       <c r="E38" t="n">
-        <v>4.76</v>
+        <v>66.78</v>
       </c>
       <c r="F38" t="n">
-        <v>4.78</v>
+        <v>67.06</v>
       </c>
       <c r="G38" t="n">
-        <v>4.96</v>
+        <v>69.36</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.216</v>
+        <v>-2.4</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.222</v>
+        <v>-2.674</v>
       </c>
       <c r="J38" t="n">
-        <v>53.04</v>
+        <v>56.99</v>
       </c>
       <c r="K38" t="n">
-        <v>45.1</v>
+        <v>34.6</v>
       </c>
       <c r="L38" t="n">
-        <v>68.92</v>
+        <v>101.77</v>
       </c>
       <c r="M38" t="n">
-        <v>46.6</v>
+        <v>54.78</v>
       </c>
       <c r="N38" t="n">
-        <v>41.23</v>
+        <v>45.37</v>
       </c>
       <c r="O38" t="n">
-        <v>43.87</v>
+        <v>42.88</v>
       </c>
       <c r="P38" t="n">
-        <v>2181.66</v>
+        <v>1325.02</v>
       </c>
       <c r="Q38" t="n">
-        <v>3704.25</v>
+        <v>1249.98</v>
       </c>
       <c r="R38" t="n">
-        <v>0.59</v>
+        <v>1.06</v>
       </c>
       <c r="S38" t="n">
-        <v>4.86</v>
+        <v>68.29000000000001</v>
       </c>
       <c r="T38" t="n">
-        <v>4.86</v>
+        <v>68.79000000000001</v>
       </c>
       <c r="U38" t="n">
-        <v>4.77</v>
+        <v>67.66</v>
       </c>
       <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
@@ -3236,69 +3236,69 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>601877</v>
+        <v>601689</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>正泰电器</t>
+          <t>拓普集团</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>32.75</v>
+        <v>58.33</v>
       </c>
       <c r="D39" t="n">
-        <v>0.09</v>
+        <v>-2.11</v>
       </c>
       <c r="E39" t="n">
-        <v>31.97</v>
+        <v>58.1</v>
       </c>
       <c r="F39" t="n">
-        <v>32.71</v>
+        <v>57.93</v>
       </c>
       <c r="G39" t="n">
-        <v>34.34</v>
+        <v>59.11</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.524</v>
+        <v>-2.211</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.134</v>
+        <v>-2.677</v>
       </c>
       <c r="J39" t="n">
-        <v>29.39</v>
+        <v>51.46</v>
       </c>
       <c r="K39" t="n">
-        <v>20.08</v>
+        <v>45.6</v>
       </c>
       <c r="L39" t="n">
-        <v>48.01</v>
+        <v>63.17</v>
       </c>
       <c r="M39" t="n">
-        <v>46.98</v>
+        <v>49.46</v>
       </c>
       <c r="N39" t="n">
-        <v>45.06</v>
+        <v>42.3</v>
       </c>
       <c r="O39" t="n">
-        <v>48.96</v>
+        <v>39.42</v>
       </c>
       <c r="P39" t="n">
-        <v>2487.67</v>
+        <v>2159.99</v>
       </c>
       <c r="Q39" t="n">
-        <v>4399.3</v>
+        <v>2292.18</v>
       </c>
       <c r="R39" t="n">
-        <v>0.57</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="S39" t="n">
-        <v>32.34</v>
+        <v>58.74</v>
       </c>
       <c r="T39" t="n">
-        <v>33.06</v>
+        <v>58.85</v>
       </c>
       <c r="U39" t="n">
-        <v>32.21</v>
+        <v>57.76</v>
       </c>
       <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
@@ -3309,69 +3309,69 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>紫光国微</t>
+          <t>三花智控</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>68.48</v>
+        <v>43.78</v>
       </c>
       <c r="D40" t="n">
-        <v>-0.77</v>
+        <v>-1.13</v>
       </c>
       <c r="E40" t="n">
-        <v>66.78</v>
+        <v>42.91</v>
       </c>
       <c r="F40" t="n">
-        <v>67.06</v>
+        <v>43.09</v>
       </c>
       <c r="G40" t="n">
-        <v>69.36</v>
+        <v>44.21</v>
       </c>
       <c r="H40" t="n">
-        <v>-2.4</v>
+        <v>-1.542</v>
       </c>
       <c r="I40" t="n">
-        <v>-2.674</v>
+        <v>-1.781</v>
       </c>
       <c r="J40" t="n">
-        <v>56.99</v>
+        <v>56.91</v>
       </c>
       <c r="K40" t="n">
-        <v>34.6</v>
+        <v>43.03</v>
       </c>
       <c r="L40" t="n">
-        <v>101.77</v>
+        <v>84.67</v>
       </c>
       <c r="M40" t="n">
-        <v>54.78</v>
+        <v>53.76</v>
       </c>
       <c r="N40" t="n">
-        <v>45.37</v>
+        <v>44.84</v>
       </c>
       <c r="O40" t="n">
-        <v>42.88</v>
+        <v>42.68</v>
       </c>
       <c r="P40" t="n">
-        <v>1325.02</v>
+        <v>6438.07</v>
       </c>
       <c r="Q40" t="n">
-        <v>1249.98</v>
+        <v>7049.34</v>
       </c>
       <c r="R40" t="n">
-        <v>1.06</v>
+        <v>0.91</v>
       </c>
       <c r="S40" t="n">
-        <v>68.29000000000001</v>
+        <v>43.67</v>
       </c>
       <c r="T40" t="n">
-        <v>68.79000000000001</v>
+        <v>44.16</v>
       </c>
       <c r="U40" t="n">
-        <v>67.66</v>
+        <v>43.2</v>
       </c>
       <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
@@ -3382,69 +3382,69 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>688271</v>
+        <v>887</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>联影医疗</t>
+          <t>中鼎股份</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>112.79</v>
+        <v>18.26</v>
       </c>
       <c r="D41" t="n">
-        <v>-2.24</v>
+        <v>-0.87</v>
       </c>
       <c r="E41" t="n">
-        <v>112.87</v>
+        <v>17.92</v>
       </c>
       <c r="F41" t="n">
-        <v>112.93</v>
+        <v>18.04</v>
       </c>
       <c r="G41" t="n">
-        <v>114.74</v>
+        <v>18.34</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.955</v>
+        <v>-0.602</v>
       </c>
       <c r="I41" t="n">
-        <v>-3.362</v>
+        <v>-0.711</v>
       </c>
       <c r="J41" t="n">
-        <v>56.9</v>
+        <v>62.21</v>
       </c>
       <c r="K41" t="n">
-        <v>48.38</v>
+        <v>48.64</v>
       </c>
       <c r="L41" t="n">
-        <v>73.94</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>46.83</v>
+        <v>53.62</v>
       </c>
       <c r="N41" t="n">
-        <v>42.81</v>
+        <v>44.72</v>
       </c>
       <c r="O41" t="n">
-        <v>40.98</v>
+        <v>40.54</v>
       </c>
       <c r="P41" t="n">
-        <v>349.59</v>
+        <v>1191.12</v>
       </c>
       <c r="Q41" t="n">
-        <v>391.27</v>
+        <v>1653.82</v>
       </c>
       <c r="R41" t="n">
-        <v>0.89</v>
+        <v>0.72</v>
       </c>
       <c r="S41" t="n">
-        <v>114.33</v>
+        <v>18.16</v>
       </c>
       <c r="T41" t="n">
-        <v>114.33</v>
+        <v>18.39</v>
       </c>
       <c r="U41" t="n">
-        <v>112.79</v>
+        <v>18.11</v>
       </c>
       <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
@@ -3455,69 +3455,69 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>688608</v>
+        <v>603236</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>恒玄科技</t>
+          <t>移远通信</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>166.01</v>
+        <v>75.87</v>
       </c>
       <c r="D42" t="n">
-        <v>-3.18</v>
+        <v>-0.76</v>
       </c>
       <c r="E42" t="n">
-        <v>165.5</v>
+        <v>74.14</v>
       </c>
       <c r="F42" t="n">
-        <v>167.1</v>
+        <v>73.78</v>
       </c>
       <c r="G42" t="n">
-        <v>169.16</v>
+        <v>75.38</v>
       </c>
       <c r="H42" t="n">
-        <v>-7.54</v>
+        <v>-2.341</v>
       </c>
       <c r="I42" t="n">
-        <v>-9.201000000000001</v>
+        <v>-2.994</v>
       </c>
       <c r="J42" t="n">
-        <v>42.65</v>
+        <v>66.91</v>
       </c>
       <c r="K42" t="n">
-        <v>42.2</v>
+        <v>49.3</v>
       </c>
       <c r="L42" t="n">
-        <v>43.57</v>
+        <v>102.12</v>
       </c>
       <c r="M42" t="n">
-        <v>46.46</v>
+        <v>58.04</v>
       </c>
       <c r="N42" t="n">
-        <v>42.42</v>
+        <v>47.74</v>
       </c>
       <c r="O42" t="n">
-        <v>39.94</v>
+        <v>41.98</v>
       </c>
       <c r="P42" t="n">
-        <v>346.52</v>
+        <v>439.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>317.44</v>
+        <v>494.34</v>
       </c>
       <c r="R42" t="n">
-        <v>1.09</v>
+        <v>0.89</v>
       </c>
       <c r="S42" t="n">
-        <v>168.04</v>
+        <v>75.7</v>
       </c>
       <c r="T42" t="n">
-        <v>168.98</v>
+        <v>76.27</v>
       </c>
       <c r="U42" t="n">
-        <v>165.5</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
@@ -3528,69 +3528,69 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>688099</v>
+        <v>603072</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>晶晨股份</t>
+          <t>天和磁材</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>80.54000000000001</v>
+        <v>36.47</v>
       </c>
       <c r="D43" t="n">
-        <v>-2.32</v>
+        <v>-0.52</v>
       </c>
       <c r="E43" t="n">
-        <v>78.29000000000001</v>
+        <v>35.99</v>
       </c>
       <c r="F43" t="n">
-        <v>79.29000000000001</v>
+        <v>35.96</v>
       </c>
       <c r="G43" t="n">
-        <v>83.28</v>
+        <v>36.9</v>
       </c>
       <c r="H43" t="n">
-        <v>-2.642</v>
+        <v>-1.357</v>
       </c>
       <c r="I43" t="n">
-        <v>-2.518</v>
+        <v>-1.564</v>
       </c>
       <c r="J43" t="n">
-        <v>45.41</v>
+        <v>70.56</v>
       </c>
       <c r="K43" t="n">
-        <v>29.61</v>
+        <v>57.88</v>
       </c>
       <c r="L43" t="n">
-        <v>77</v>
+        <v>95.91</v>
       </c>
       <c r="M43" t="n">
-        <v>51.12</v>
+        <v>52.19</v>
       </c>
       <c r="N43" t="n">
-        <v>45.56</v>
+        <v>43.02</v>
       </c>
       <c r="O43" t="n">
-        <v>45.21</v>
+        <v>41.44</v>
       </c>
       <c r="P43" t="n">
-        <v>696.64</v>
+        <v>285.19</v>
       </c>
       <c r="Q43" t="n">
-        <v>1017.54</v>
+        <v>223.75</v>
       </c>
       <c r="R43" t="n">
-        <v>0.68</v>
+        <v>1.27</v>
       </c>
       <c r="S43" t="n">
-        <v>81.55</v>
+        <v>36.5</v>
       </c>
       <c r="T43" t="n">
-        <v>82.09</v>
+        <v>36.93</v>
       </c>
       <c r="U43" t="n">
-        <v>80.5</v>
+        <v>36.25</v>
       </c>
       <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
@@ -3601,69 +3601,69 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>688332</v>
+        <v>301023</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>中科蓝讯</t>
+          <t>奕帆传动</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>124.69</v>
+        <v>39.69</v>
       </c>
       <c r="D44" t="n">
-        <v>-3.41</v>
+        <v>-1.1</v>
       </c>
       <c r="E44" t="n">
-        <v>122.9</v>
+        <v>38.67</v>
       </c>
       <c r="F44" t="n">
-        <v>119.85</v>
+        <v>38.76</v>
       </c>
       <c r="G44" t="n">
-        <v>120.26</v>
+        <v>40</v>
       </c>
       <c r="H44" t="n">
-        <v>-1.748</v>
+        <v>-1.417</v>
       </c>
       <c r="I44" t="n">
-        <v>-3.401</v>
+        <v>-1.621</v>
       </c>
       <c r="J44" t="n">
-        <v>78.95999999999999</v>
+        <v>57.47</v>
       </c>
       <c r="K44" t="n">
-        <v>71.87</v>
+        <v>40.11</v>
       </c>
       <c r="L44" t="n">
-        <v>93.14</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>59.86</v>
+        <v>54.65</v>
       </c>
       <c r="N44" t="n">
-        <v>53.25</v>
+        <v>46.23</v>
       </c>
       <c r="O44" t="n">
-        <v>48.08</v>
+        <v>45.13</v>
       </c>
       <c r="P44" t="n">
-        <v>419.77</v>
+        <v>140.83</v>
       </c>
       <c r="Q44" t="n">
-        <v>152.99</v>
+        <v>124.52</v>
       </c>
       <c r="R44" t="n">
-        <v>2.74</v>
+        <v>1.13</v>
       </c>
       <c r="S44" t="n">
-        <v>129.84</v>
+        <v>40.17</v>
       </c>
       <c r="T44" t="n">
-        <v>131.08</v>
+        <v>40.63</v>
       </c>
       <c r="U44" t="n">
-        <v>124.6</v>
+        <v>39.48</v>
       </c>
       <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
@@ -3674,69 +3674,69 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>688049</v>
+        <v>2074</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>炬芯科技</t>
+          <t>国轩高科</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>45.5</v>
+        <v>35.28</v>
       </c>
       <c r="D45" t="n">
-        <v>-2.32</v>
+        <v>0.31</v>
       </c>
       <c r="E45" t="n">
-        <v>44.71</v>
+        <v>34.5</v>
       </c>
       <c r="F45" t="n">
-        <v>44.82</v>
+        <v>35.57</v>
       </c>
       <c r="G45" t="n">
-        <v>46.15</v>
+        <v>36.65</v>
       </c>
       <c r="H45" t="n">
-        <v>-1.676</v>
+        <v>-0.833</v>
       </c>
       <c r="I45" t="n">
-        <v>-1.955</v>
+        <v>-0.627</v>
       </c>
       <c r="J45" t="n">
-        <v>54.71</v>
+        <v>27.28</v>
       </c>
       <c r="K45" t="n">
-        <v>40.84</v>
+        <v>24.49</v>
       </c>
       <c r="L45" t="n">
-        <v>82.47</v>
+        <v>32.87</v>
       </c>
       <c r="M45" t="n">
-        <v>51.54</v>
+        <v>46.46</v>
       </c>
       <c r="N45" t="n">
-        <v>44.97</v>
+        <v>42.58</v>
       </c>
       <c r="O45" t="n">
-        <v>42.84</v>
+        <v>42.97</v>
       </c>
       <c r="P45" t="n">
-        <v>496.24</v>
+        <v>2581.22</v>
       </c>
       <c r="Q45" t="n">
-        <v>427.43</v>
+        <v>3875.59</v>
       </c>
       <c r="R45" t="n">
-        <v>1.16</v>
+        <v>0.67</v>
       </c>
       <c r="S45" t="n">
-        <v>45.9</v>
+        <v>34.92</v>
       </c>
       <c r="T45" t="n">
-        <v>46.35</v>
+        <v>35.58</v>
       </c>
       <c r="U45" t="n">
-        <v>45.39</v>
+        <v>34.58</v>
       </c>
       <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
@@ -3747,69 +3747,69 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>601689</v>
+        <v>300450</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>拓普集团</t>
+          <t>先导智能</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>58.33</v>
+        <v>50.28</v>
       </c>
       <c r="D46" t="n">
-        <v>-2.11</v>
+        <v>-1.24</v>
       </c>
       <c r="E46" t="n">
-        <v>58.1</v>
+        <v>48.46</v>
       </c>
       <c r="F46" t="n">
-        <v>57.93</v>
+        <v>48.57</v>
       </c>
       <c r="G46" t="n">
-        <v>59.11</v>
+        <v>49.03</v>
       </c>
       <c r="H46" t="n">
-        <v>-2.211</v>
+        <v>-0.979</v>
       </c>
       <c r="I46" t="n">
-        <v>-2.677</v>
+        <v>-1.391</v>
       </c>
       <c r="J46" t="n">
-        <v>51.46</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>45.6</v>
+        <v>51.29</v>
       </c>
       <c r="L46" t="n">
-        <v>63.17</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>49.46</v>
+        <v>61.46</v>
       </c>
       <c r="N46" t="n">
-        <v>42.3</v>
+        <v>52.7</v>
       </c>
       <c r="O46" t="n">
-        <v>39.42</v>
+        <v>48.41</v>
       </c>
       <c r="P46" t="n">
-        <v>2159.99</v>
+        <v>3918.17</v>
       </c>
       <c r="Q46" t="n">
-        <v>2292.18</v>
+        <v>4482.97</v>
       </c>
       <c r="R46" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.87</v>
       </c>
       <c r="S46" t="n">
-        <v>58.74</v>
+        <v>50.25</v>
       </c>
       <c r="T46" t="n">
-        <v>58.85</v>
+        <v>50.96</v>
       </c>
       <c r="U46" t="n">
-        <v>57.76</v>
+        <v>49.68</v>
       </c>
       <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
@@ -3820,69 +3820,69 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2050</v>
+        <v>603200</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>三花智控</t>
+          <t>上海洗霸</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>43.78</v>
+        <v>56.1</v>
       </c>
       <c r="D47" t="n">
-        <v>-1.13</v>
+        <v>-3.26</v>
       </c>
       <c r="E47" t="n">
-        <v>42.91</v>
+        <v>56.7</v>
       </c>
       <c r="F47" t="n">
-        <v>43.09</v>
+        <v>57.54</v>
       </c>
       <c r="G47" t="n">
-        <v>44.21</v>
+        <v>60.25</v>
       </c>
       <c r="H47" t="n">
-        <v>-1.542</v>
+        <v>-4.319</v>
       </c>
       <c r="I47" t="n">
-        <v>-1.781</v>
+        <v>-4.638</v>
       </c>
       <c r="J47" t="n">
-        <v>56.91</v>
+        <v>23.95</v>
       </c>
       <c r="K47" t="n">
-        <v>43.03</v>
+        <v>26.83</v>
       </c>
       <c r="L47" t="n">
-        <v>84.67</v>
+        <v>18.19</v>
       </c>
       <c r="M47" t="n">
-        <v>53.76</v>
+        <v>35.94</v>
       </c>
       <c r="N47" t="n">
-        <v>44.84</v>
+        <v>31.06</v>
       </c>
       <c r="O47" t="n">
-        <v>42.68</v>
+        <v>32.83</v>
       </c>
       <c r="P47" t="n">
-        <v>6438.07</v>
+        <v>608.74</v>
       </c>
       <c r="Q47" t="n">
-        <v>7049.34</v>
+        <v>525.48</v>
       </c>
       <c r="R47" t="n">
-        <v>0.91</v>
+        <v>1.16</v>
       </c>
       <c r="S47" t="n">
-        <v>43.67</v>
+        <v>57.34</v>
       </c>
       <c r="T47" t="n">
-        <v>44.16</v>
+        <v>57.6</v>
       </c>
       <c r="U47" t="n">
-        <v>43.2</v>
+        <v>55.99</v>
       </c>
       <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
@@ -3893,69 +3893,69 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>887</v>
+        <v>300409</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>中鼎股份</t>
+          <t>道氏技术</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>18.26</v>
+        <v>25.66</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.87</v>
+        <v>-0.74</v>
       </c>
       <c r="E48" t="n">
-        <v>17.92</v>
+        <v>24.85</v>
       </c>
       <c r="F48" t="n">
-        <v>18.04</v>
+        <v>24.89</v>
       </c>
       <c r="G48" t="n">
-        <v>18.34</v>
+        <v>25.96</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.602</v>
+        <v>-0.878</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.711</v>
+        <v>-0.975</v>
       </c>
       <c r="J48" t="n">
-        <v>62.21</v>
+        <v>61.43</v>
       </c>
       <c r="K48" t="n">
-        <v>48.64</v>
+        <v>42.24</v>
       </c>
       <c r="L48" t="n">
-        <v>89.34999999999999</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>53.62</v>
+        <v>57.18</v>
       </c>
       <c r="N48" t="n">
-        <v>44.72</v>
+        <v>47.47</v>
       </c>
       <c r="O48" t="n">
-        <v>40.54</v>
+        <v>46.43</v>
       </c>
       <c r="P48" t="n">
-        <v>1191.12</v>
+        <v>1937.48</v>
       </c>
       <c r="Q48" t="n">
-        <v>1653.82</v>
+        <v>3274.01</v>
       </c>
       <c r="R48" t="n">
-        <v>0.72</v>
+        <v>0.59</v>
       </c>
       <c r="S48" t="n">
-        <v>18.16</v>
+        <v>25.5</v>
       </c>
       <c r="T48" t="n">
-        <v>18.39</v>
+        <v>25.89</v>
       </c>
       <c r="U48" t="n">
-        <v>18.11</v>
+        <v>25.43</v>
       </c>
       <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
@@ -3966,69 +3966,69 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>603236</v>
+        <v>2202</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>移远通信</t>
+          <t>金风科技</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>75.87</v>
+        <v>23.84</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.76</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>74.14</v>
+        <v>23.76</v>
       </c>
       <c r="F49" t="n">
-        <v>73.78</v>
+        <v>25.38</v>
       </c>
       <c r="G49" t="n">
-        <v>75.38</v>
+        <v>27.47</v>
       </c>
       <c r="H49" t="n">
-        <v>-2.341</v>
+        <v>-1.107</v>
       </c>
       <c r="I49" t="n">
-        <v>-2.994</v>
+        <v>-0.509</v>
       </c>
       <c r="J49" t="n">
-        <v>66.91</v>
+        <v>14.09</v>
       </c>
       <c r="K49" t="n">
-        <v>49.3</v>
+        <v>12.53</v>
       </c>
       <c r="L49" t="n">
-        <v>102.12</v>
+        <v>17.2</v>
       </c>
       <c r="M49" t="n">
-        <v>58.04</v>
+        <v>31.03</v>
       </c>
       <c r="N49" t="n">
-        <v>47.74</v>
+        <v>35.83</v>
       </c>
       <c r="O49" t="n">
-        <v>41.98</v>
+        <v>43.71</v>
       </c>
       <c r="P49" t="n">
-        <v>439.28</v>
+        <v>21323.37</v>
       </c>
       <c r="Q49" t="n">
-        <v>494.34</v>
+        <v>27669.12</v>
       </c>
       <c r="R49" t="n">
-        <v>0.89</v>
+        <v>0.77</v>
       </c>
       <c r="S49" t="n">
-        <v>75.7</v>
+        <v>23.42</v>
       </c>
       <c r="T49" t="n">
-        <v>76.27</v>
+        <v>24.2</v>
       </c>
       <c r="U49" t="n">
-        <v>74.73999999999999</v>
+        <v>23.01</v>
       </c>
       <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
@@ -4039,69 +4039,69 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>603072</v>
+        <v>600990</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>天和磁材</t>
+          <t>四创电子</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>36.47</v>
+        <v>23.08</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.52</v>
+        <v>2.17</v>
       </c>
       <c r="E50" t="n">
-        <v>35.99</v>
+        <v>22.26</v>
       </c>
       <c r="F50" t="n">
-        <v>35.96</v>
+        <v>22.47</v>
       </c>
       <c r="G50" t="n">
-        <v>36.9</v>
+        <v>23.22</v>
       </c>
       <c r="H50" t="n">
-        <v>-1.357</v>
+        <v>-1.046</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.564</v>
+        <v>-1.179</v>
       </c>
       <c r="J50" t="n">
-        <v>70.56</v>
+        <v>44.48</v>
       </c>
       <c r="K50" t="n">
-        <v>57.88</v>
+        <v>30.75</v>
       </c>
       <c r="L50" t="n">
-        <v>95.91</v>
+        <v>71.95</v>
       </c>
       <c r="M50" t="n">
-        <v>52.19</v>
+        <v>58.19</v>
       </c>
       <c r="N50" t="n">
-        <v>43.02</v>
+        <v>45.12</v>
       </c>
       <c r="O50" t="n">
-        <v>41.44</v>
+        <v>41.01</v>
       </c>
       <c r="P50" t="n">
-        <v>285.19</v>
+        <v>831.02</v>
       </c>
       <c r="Q50" t="n">
-        <v>223.75</v>
+        <v>421.03</v>
       </c>
       <c r="R50" t="n">
-        <v>1.27</v>
+        <v>1.97</v>
       </c>
       <c r="S50" t="n">
-        <v>36.5</v>
+        <v>22.5</v>
       </c>
       <c r="T50" t="n">
-        <v>36.93</v>
+        <v>23.51</v>
       </c>
       <c r="U50" t="n">
-        <v>36.25</v>
+        <v>22.39</v>
       </c>
       <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
@@ -4112,69 +4112,69 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>301023</v>
+        <v>2025</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>奕帆传动</t>
+          <t>航天电器</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>39.69</v>
+        <v>78.22</v>
       </c>
       <c r="D51" t="n">
-        <v>-1.1</v>
+        <v>10</v>
       </c>
       <c r="E51" t="n">
-        <v>38.67</v>
+        <v>67.45999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>38.76</v>
+        <v>65.8</v>
       </c>
       <c r="G51" t="n">
-        <v>40</v>
+        <v>63.27</v>
       </c>
       <c r="H51" t="n">
-        <v>-1.417</v>
+        <v>3.932</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.621</v>
+        <v>2.952</v>
       </c>
       <c r="J51" t="n">
-        <v>57.47</v>
+        <v>77.55</v>
       </c>
       <c r="K51" t="n">
-        <v>40.11</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>92.18000000000001</v>
+        <v>103.46</v>
       </c>
       <c r="M51" t="n">
-        <v>54.65</v>
+        <v>79.41</v>
       </c>
       <c r="N51" t="n">
-        <v>46.23</v>
+        <v>71.86</v>
       </c>
       <c r="O51" t="n">
-        <v>45.13</v>
+        <v>66.59</v>
       </c>
       <c r="P51" t="n">
-        <v>140.83</v>
+        <v>2684.39</v>
       </c>
       <c r="Q51" t="n">
-        <v>124.52</v>
+        <v>3617.51</v>
       </c>
       <c r="R51" t="n">
-        <v>1.13</v>
+        <v>0.74</v>
       </c>
       <c r="S51" t="n">
-        <v>40.17</v>
+        <v>70.39</v>
       </c>
       <c r="T51" t="n">
-        <v>40.63</v>
+        <v>78.22</v>
       </c>
       <c r="U51" t="n">
-        <v>39.48</v>
+        <v>70.39</v>
       </c>
       <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
@@ -4185,69 +4185,69 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2074</v>
+        <v>600584</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>国轩高科</t>
+          <t>长电科技</t>
         </is>
       </c>
       <c r="C52" t="n">
+        <v>41.91</v>
+      </c>
+      <c r="D52" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E52" t="n">
+        <v>39.9</v>
+      </c>
+      <c r="F52" t="n">
+        <v>39.65</v>
+      </c>
+      <c r="G52" t="n">
+        <v>41.42</v>
+      </c>
+      <c r="H52" t="n">
+        <v>-1.38</v>
+      </c>
+      <c r="I52" t="n">
+        <v>-1.599</v>
+      </c>
+      <c r="J52" t="n">
+        <v>58.19</v>
+      </c>
+      <c r="K52" t="n">
         <v>35.28</v>
       </c>
-      <c r="D52" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="E52" t="n">
-        <v>34.5</v>
-      </c>
-      <c r="F52" t="n">
-        <v>35.57</v>
-      </c>
-      <c r="G52" t="n">
-        <v>36.65</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-0.833</v>
-      </c>
-      <c r="I52" t="n">
-        <v>-0.627</v>
-      </c>
-      <c r="J52" t="n">
-        <v>27.28</v>
-      </c>
-      <c r="K52" t="n">
-        <v>24.49</v>
-      </c>
       <c r="L52" t="n">
-        <v>32.87</v>
+        <v>104.02</v>
       </c>
       <c r="M52" t="n">
-        <v>46.46</v>
+        <v>64.23999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>42.58</v>
+        <v>50.95</v>
       </c>
       <c r="O52" t="n">
-        <v>42.97</v>
+        <v>48.34</v>
       </c>
       <c r="P52" t="n">
-        <v>2581.22</v>
+        <v>4975.33</v>
       </c>
       <c r="Q52" t="n">
-        <v>3875.59</v>
+        <v>5150.97</v>
       </c>
       <c r="R52" t="n">
-        <v>0.67</v>
+        <v>0.97</v>
       </c>
       <c r="S52" t="n">
-        <v>34.92</v>
+        <v>41.17</v>
       </c>
       <c r="T52" t="n">
-        <v>35.58</v>
+        <v>42.47</v>
       </c>
       <c r="U52" t="n">
-        <v>34.58</v>
+        <v>41.05</v>
       </c>
       <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
@@ -4258,69 +4258,69 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>300450</v>
+        <v>300759</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>先导智能</t>
+          <t>康龙化成</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>50.28</v>
+        <v>30.55</v>
       </c>
       <c r="D53" t="n">
-        <v>-1.24</v>
+        <v>0.49</v>
       </c>
       <c r="E53" t="n">
-        <v>48.46</v>
+        <v>30.35</v>
       </c>
       <c r="F53" t="n">
-        <v>48.57</v>
+        <v>28.89</v>
       </c>
       <c r="G53" t="n">
-        <v>49.03</v>
+        <v>27.92</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.979</v>
+        <v>0.531</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.391</v>
+        <v>-0.003</v>
       </c>
       <c r="J53" t="n">
-        <v>65.59999999999999</v>
+        <v>81.69</v>
       </c>
       <c r="K53" t="n">
-        <v>51.29</v>
+        <v>75.94</v>
       </c>
       <c r="L53" t="n">
-        <v>94.20999999999999</v>
+        <v>93.19</v>
       </c>
       <c r="M53" t="n">
-        <v>61.46</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="N53" t="n">
-        <v>52.7</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>48.41</v>
+        <v>57.8</v>
       </c>
       <c r="P53" t="n">
-        <v>3918.17</v>
+        <v>4591.4</v>
       </c>
       <c r="Q53" t="n">
-        <v>4482.97</v>
+        <v>3456.98</v>
       </c>
       <c r="R53" t="n">
-        <v>0.87</v>
+        <v>1.33</v>
       </c>
       <c r="S53" t="n">
-        <v>50.25</v>
+        <v>30.2</v>
       </c>
       <c r="T53" t="n">
-        <v>50.96</v>
+        <v>31.66</v>
       </c>
       <c r="U53" t="n">
-        <v>49.68</v>
+        <v>30.13</v>
       </c>
       <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
@@ -4331,69 +4331,69 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>688778</v>
+        <v>301333</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>厦钨新能</t>
+          <t>诺思格</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>72.12</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>-2.62</v>
+        <v>-0.46</v>
       </c>
       <c r="E54" t="n">
-        <v>71.15000000000001</v>
+        <v>67.28</v>
       </c>
       <c r="F54" t="n">
-        <v>72.43000000000001</v>
+        <v>66.25</v>
       </c>
       <c r="G54" t="n">
-        <v>73.09999999999999</v>
+        <v>63.38</v>
       </c>
       <c r="H54" t="n">
-        <v>-2.033</v>
+        <v>0.063</v>
       </c>
       <c r="I54" t="n">
-        <v>-2.351</v>
+        <v>-0.9360000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>46.06</v>
+        <v>62.92</v>
       </c>
       <c r="K54" t="n">
-        <v>46.26</v>
+        <v>64.67</v>
       </c>
       <c r="L54" t="n">
-        <v>45.67</v>
+        <v>59.42</v>
       </c>
       <c r="M54" t="n">
-        <v>49.22</v>
+        <v>58.21</v>
       </c>
       <c r="N54" t="n">
-        <v>45.42</v>
+        <v>54.34</v>
       </c>
       <c r="O54" t="n">
-        <v>44.52</v>
+        <v>51.34</v>
       </c>
       <c r="P54" t="n">
-        <v>427.08</v>
+        <v>188.36</v>
       </c>
       <c r="Q54" t="n">
-        <v>503.05</v>
+        <v>243.66</v>
       </c>
       <c r="R54" t="n">
-        <v>0.85</v>
+        <v>0.77</v>
       </c>
       <c r="S54" t="n">
-        <v>74</v>
+        <v>67.11</v>
       </c>
       <c r="T54" t="n">
-        <v>74.18000000000001</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="U54" t="n">
-        <v>71.86</v>
+        <v>66.92</v>
       </c>
       <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
@@ -4404,69 +4404,69 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>688116</v>
+        <v>963</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>天奈科技</t>
+          <t>华东医药</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>38.88</v>
+        <v>35.95</v>
       </c>
       <c r="D55" t="n">
-        <v>-1.97</v>
+        <v>-0.83</v>
       </c>
       <c r="E55" t="n">
-        <v>38.28</v>
+        <v>36.26</v>
       </c>
       <c r="F55" t="n">
-        <v>39.35</v>
+        <v>35.75</v>
       </c>
       <c r="G55" t="n">
-        <v>40.68</v>
+        <v>35.36</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.575</v>
+        <v>0.125</v>
       </c>
       <c r="I55" t="n">
-        <v>-1.562</v>
+        <v>-0.082</v>
       </c>
       <c r="J55" t="n">
-        <v>35.64</v>
+        <v>74.13</v>
       </c>
       <c r="K55" t="n">
-        <v>30.01</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>46.91</v>
+        <v>76.69</v>
       </c>
       <c r="M55" t="n">
-        <v>44.22</v>
+        <v>53.39</v>
       </c>
       <c r="N55" t="n">
-        <v>39.59</v>
+        <v>53.07</v>
       </c>
       <c r="O55" t="n">
-        <v>39.14</v>
+        <v>49.34</v>
       </c>
       <c r="P55" t="n">
-        <v>584.92</v>
+        <v>1288.95</v>
       </c>
       <c r="Q55" t="n">
-        <v>747.83</v>
+        <v>1105.28</v>
       </c>
       <c r="R55" t="n">
-        <v>0.78</v>
+        <v>1.17</v>
       </c>
       <c r="S55" t="n">
-        <v>39.1</v>
+        <v>36.09</v>
       </c>
       <c r="T55" t="n">
-        <v>39.73</v>
+        <v>36.43</v>
       </c>
       <c r="U55" t="n">
-        <v>38.79</v>
+        <v>35.66</v>
       </c>
       <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
@@ -4477,69 +4477,69 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>603200</v>
+        <v>603658</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>上海洗霸</t>
+          <t>安图生物</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>56.1</v>
+        <v>34.42</v>
       </c>
       <c r="D56" t="n">
-        <v>-3.26</v>
+        <v>-1.52</v>
       </c>
       <c r="E56" t="n">
-        <v>56.7</v>
+        <v>34.49</v>
       </c>
       <c r="F56" t="n">
-        <v>57.54</v>
+        <v>33.99</v>
       </c>
       <c r="G56" t="n">
-        <v>60.25</v>
+        <v>34.11</v>
       </c>
       <c r="H56" t="n">
-        <v>-4.319</v>
+        <v>-0.252</v>
       </c>
       <c r="I56" t="n">
-        <v>-4.638</v>
+        <v>-0.455</v>
       </c>
       <c r="J56" t="n">
-        <v>23.95</v>
+        <v>79.28</v>
       </c>
       <c r="K56" t="n">
-        <v>26.83</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>18.19</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>35.94</v>
+        <v>54.26</v>
       </c>
       <c r="N56" t="n">
-        <v>31.06</v>
+        <v>50.21</v>
       </c>
       <c r="O56" t="n">
-        <v>32.83</v>
+        <v>46.69</v>
       </c>
       <c r="P56" t="n">
-        <v>608.74</v>
+        <v>177.53</v>
       </c>
       <c r="Q56" t="n">
-        <v>525.48</v>
+        <v>200.93</v>
       </c>
       <c r="R56" t="n">
-        <v>1.16</v>
+        <v>0.88</v>
       </c>
       <c r="S56" t="n">
-        <v>57.34</v>
+        <v>34.77</v>
       </c>
       <c r="T56" t="n">
-        <v>57.6</v>
+        <v>35.12</v>
       </c>
       <c r="U56" t="n">
-        <v>55.99</v>
+        <v>34.4</v>
       </c>
       <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
@@ -4550,1021 +4550,72 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>300409</v>
+        <v>300357</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>道氏技术</t>
+          <t>我武生物</t>
         </is>
       </c>
       <c r="C57" t="n">
+        <v>26.18</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="E57" t="n">
+        <v>25.96</v>
+      </c>
+      <c r="F57" t="n">
+        <v>25.71</v>
+      </c>
+      <c r="G57" t="n">
+        <v>25.27</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I57" t="n">
+        <v>-0.291</v>
+      </c>
+      <c r="J57" t="n">
+        <v>75.75</v>
+      </c>
+      <c r="K57" t="n">
+        <v>72.17</v>
+      </c>
+      <c r="L57" t="n">
+        <v>82.92</v>
+      </c>
+      <c r="M57" t="n">
+        <v>62.2</v>
+      </c>
+      <c r="N57" t="n">
+        <v>55.63</v>
+      </c>
+      <c r="O57" t="n">
+        <v>49.34</v>
+      </c>
+      <c r="P57" t="n">
+        <v>1324.23</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>1198.95</v>
+      </c>
+      <c r="R57" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25.76</v>
+      </c>
+      <c r="T57" t="n">
+        <v>26.88</v>
+      </c>
+      <c r="U57" t="n">
         <v>25.66</v>
-      </c>
-      <c r="D57" t="n">
-        <v>-0.74</v>
-      </c>
-      <c r="E57" t="n">
-        <v>24.85</v>
-      </c>
-      <c r="F57" t="n">
-        <v>24.89</v>
-      </c>
-      <c r="G57" t="n">
-        <v>25.96</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-0.878</v>
-      </c>
-      <c r="I57" t="n">
-        <v>-0.975</v>
-      </c>
-      <c r="J57" t="n">
-        <v>61.43</v>
-      </c>
-      <c r="K57" t="n">
-        <v>42.24</v>
-      </c>
-      <c r="L57" t="n">
-        <v>99.81999999999999</v>
-      </c>
-      <c r="M57" t="n">
-        <v>57.18</v>
-      </c>
-      <c r="N57" t="n">
-        <v>47.47</v>
-      </c>
-      <c r="O57" t="n">
-        <v>46.43</v>
-      </c>
-      <c r="P57" t="n">
-        <v>1937.48</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>3274.01</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="S57" t="n">
-        <v>25.5</v>
-      </c>
-      <c r="T57" t="n">
-        <v>25.89</v>
-      </c>
-      <c r="U57" t="n">
-        <v>25.43</v>
       </c>
       <c r="V57" t="inlineStr"/>
       <c r="W57" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2202</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>金风科技</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>23.84</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>23.76</v>
-      </c>
-      <c r="F58" t="n">
-        <v>25.38</v>
-      </c>
-      <c r="G58" t="n">
-        <v>27.47</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-1.107</v>
-      </c>
-      <c r="I58" t="n">
-        <v>-0.509</v>
-      </c>
-      <c r="J58" t="n">
-        <v>14.09</v>
-      </c>
-      <c r="K58" t="n">
-        <v>12.53</v>
-      </c>
-      <c r="L58" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="M58" t="n">
-        <v>31.03</v>
-      </c>
-      <c r="N58" t="n">
-        <v>35.83</v>
-      </c>
-      <c r="O58" t="n">
-        <v>43.71</v>
-      </c>
-      <c r="P58" t="n">
-        <v>21323.37</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>27669.12</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="S58" t="n">
-        <v>23.42</v>
-      </c>
-      <c r="T58" t="n">
-        <v>24.2</v>
-      </c>
-      <c r="U58" t="n">
-        <v>23.01</v>
-      </c>
-      <c r="V58" t="inlineStr"/>
-      <c r="W58" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>688066</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>航天宏图</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>18.86</v>
-      </c>
-      <c r="D59" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="E59" t="n">
-        <v>17.87</v>
-      </c>
-      <c r="F59" t="n">
-        <v>18.81</v>
-      </c>
-      <c r="G59" t="n">
-        <v>20.29</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-1.972</v>
-      </c>
-      <c r="I59" t="n">
-        <v>-2.048</v>
-      </c>
-      <c r="J59" t="n">
-        <v>33.53</v>
-      </c>
-      <c r="K59" t="n">
-        <v>20.18</v>
-      </c>
-      <c r="L59" t="n">
-        <v>60.21</v>
-      </c>
-      <c r="M59" t="n">
-        <v>47.88</v>
-      </c>
-      <c r="N59" t="n">
-        <v>39.49</v>
-      </c>
-      <c r="O59" t="n">
-        <v>39.43</v>
-      </c>
-      <c r="P59" t="n">
-        <v>1539.76</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>1069.66</v>
-      </c>
-      <c r="R59" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S59" t="n">
-        <v>18.75</v>
-      </c>
-      <c r="T59" t="n">
-        <v>19.65</v>
-      </c>
-      <c r="U59" t="n">
-        <v>18.4</v>
-      </c>
-      <c r="V59" t="inlineStr"/>
-      <c r="W59" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>600990</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>四创电子</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>23.08</v>
-      </c>
-      <c r="D60" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="E60" t="n">
-        <v>22.26</v>
-      </c>
-      <c r="F60" t="n">
-        <v>22.47</v>
-      </c>
-      <c r="G60" t="n">
-        <v>23.22</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-1.046</v>
-      </c>
-      <c r="I60" t="n">
-        <v>-1.179</v>
-      </c>
-      <c r="J60" t="n">
-        <v>44.48</v>
-      </c>
-      <c r="K60" t="n">
-        <v>30.75</v>
-      </c>
-      <c r="L60" t="n">
-        <v>71.95</v>
-      </c>
-      <c r="M60" t="n">
-        <v>58.19</v>
-      </c>
-      <c r="N60" t="n">
-        <v>45.12</v>
-      </c>
-      <c r="O60" t="n">
-        <v>41.01</v>
-      </c>
-      <c r="P60" t="n">
-        <v>831.02</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>421.03</v>
-      </c>
-      <c r="R60" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="S60" t="n">
-        <v>22.5</v>
-      </c>
-      <c r="T60" t="n">
-        <v>23.51</v>
-      </c>
-      <c r="U60" t="n">
-        <v>22.39</v>
-      </c>
-      <c r="V60" t="inlineStr"/>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2025</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>航天电器</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>78.22</v>
-      </c>
-      <c r="D61" t="n">
-        <v>10</v>
-      </c>
-      <c r="E61" t="n">
-        <v>67.45999999999999</v>
-      </c>
-      <c r="F61" t="n">
-        <v>65.8</v>
-      </c>
-      <c r="G61" t="n">
-        <v>63.27</v>
-      </c>
-      <c r="H61" t="n">
-        <v>3.932</v>
-      </c>
-      <c r="I61" t="n">
-        <v>2.952</v>
-      </c>
-      <c r="J61" t="n">
-        <v>77.55</v>
-      </c>
-      <c r="K61" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="L61" t="n">
-        <v>103.46</v>
-      </c>
-      <c r="M61" t="n">
-        <v>79.41</v>
-      </c>
-      <c r="N61" t="n">
-        <v>71.86</v>
-      </c>
-      <c r="O61" t="n">
-        <v>66.59</v>
-      </c>
-      <c r="P61" t="n">
-        <v>2684.39</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>3617.51</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="S61" t="n">
-        <v>70.39</v>
-      </c>
-      <c r="T61" t="n">
-        <v>78.22</v>
-      </c>
-      <c r="U61" t="n">
-        <v>70.39</v>
-      </c>
-      <c r="V61" t="inlineStr"/>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>600584</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>长电科技</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>41.91</v>
-      </c>
-      <c r="D62" t="n">
-        <v>-0.17</v>
-      </c>
-      <c r="E62" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="F62" t="n">
-        <v>39.65</v>
-      </c>
-      <c r="G62" t="n">
-        <v>41.42</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-1.38</v>
-      </c>
-      <c r="I62" t="n">
-        <v>-1.599</v>
-      </c>
-      <c r="J62" t="n">
-        <v>58.19</v>
-      </c>
-      <c r="K62" t="n">
-        <v>35.28</v>
-      </c>
-      <c r="L62" t="n">
-        <v>104.02</v>
-      </c>
-      <c r="M62" t="n">
-        <v>64.23999999999999</v>
-      </c>
-      <c r="N62" t="n">
-        <v>50.95</v>
-      </c>
-      <c r="O62" t="n">
-        <v>48.34</v>
-      </c>
-      <c r="P62" t="n">
-        <v>4975.33</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>5150.97</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.97</v>
-      </c>
-      <c r="S62" t="n">
-        <v>41.17</v>
-      </c>
-      <c r="T62" t="n">
-        <v>42.47</v>
-      </c>
-      <c r="U62" t="n">
-        <v>41.05</v>
-      </c>
-      <c r="V62" t="inlineStr"/>
-      <c r="W62" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>688295</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>中复神鹰</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>50.48</v>
-      </c>
-      <c r="D63" t="n">
-        <v>-3.03</v>
-      </c>
-      <c r="E63" t="n">
-        <v>50.76</v>
-      </c>
-      <c r="F63" t="n">
-        <v>53.72</v>
-      </c>
-      <c r="G63" t="n">
-        <v>54.55</v>
-      </c>
-      <c r="H63" t="n">
-        <v>3.158</v>
-      </c>
-      <c r="I63" t="n">
-        <v>4.768</v>
-      </c>
-      <c r="J63" t="n">
-        <v>16.93</v>
-      </c>
-      <c r="K63" t="n">
-        <v>21.1</v>
-      </c>
-      <c r="L63" t="n">
-        <v>8.59</v>
-      </c>
-      <c r="M63" t="n">
-        <v>40.46</v>
-      </c>
-      <c r="N63" t="n">
-        <v>50.69</v>
-      </c>
-      <c r="O63" t="n">
-        <v>56.73</v>
-      </c>
-      <c r="P63" t="n">
-        <v>1522.41</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>2887.96</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="S63" t="n">
-        <v>51.33</v>
-      </c>
-      <c r="T63" t="n">
-        <v>51.44</v>
-      </c>
-      <c r="U63" t="n">
-        <v>49.68</v>
-      </c>
-      <c r="V63" t="inlineStr"/>
-      <c r="W63" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>300759</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>康龙化成</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>30.55</v>
-      </c>
-      <c r="D64" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="E64" t="n">
-        <v>30.35</v>
-      </c>
-      <c r="F64" t="n">
-        <v>28.89</v>
-      </c>
-      <c r="G64" t="n">
-        <v>27.92</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.531</v>
-      </c>
-      <c r="I64" t="n">
-        <v>-0.003</v>
-      </c>
-      <c r="J64" t="n">
-        <v>81.69</v>
-      </c>
-      <c r="K64" t="n">
-        <v>75.94</v>
-      </c>
-      <c r="L64" t="n">
-        <v>93.19</v>
-      </c>
-      <c r="M64" t="n">
-        <v>76.29000000000001</v>
-      </c>
-      <c r="N64" t="n">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="O64" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="P64" t="n">
-        <v>4591.4</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>3456.98</v>
-      </c>
-      <c r="R64" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S64" t="n">
-        <v>30.2</v>
-      </c>
-      <c r="T64" t="n">
-        <v>31.66</v>
-      </c>
-      <c r="U64" t="n">
-        <v>30.13</v>
-      </c>
-      <c r="V64" t="inlineStr"/>
-      <c r="W64" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>688621</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>阳光诺和</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>66.62</v>
-      </c>
-      <c r="D65" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="E65" t="n">
-        <v>67.09</v>
-      </c>
-      <c r="F65" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="G65" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.8090000000000001</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.094</v>
-      </c>
-      <c r="J65" t="n">
-        <v>73.51000000000001</v>
-      </c>
-      <c r="K65" t="n">
-        <v>73.73</v>
-      </c>
-      <c r="L65" t="n">
-        <v>73.06</v>
-      </c>
-      <c r="M65" t="n">
-        <v>55.51</v>
-      </c>
-      <c r="N65" t="n">
-        <v>55.04</v>
-      </c>
-      <c r="O65" t="n">
-        <v>52.05</v>
-      </c>
-      <c r="P65" t="n">
-        <v>278.22</v>
-      </c>
-      <c r="Q65" t="n">
-        <v>241.42</v>
-      </c>
-      <c r="R65" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="S65" t="n">
-        <v>69</v>
-      </c>
-      <c r="T65" t="n">
-        <v>69.77</v>
-      </c>
-      <c r="U65" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="V65" t="inlineStr"/>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>301333</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>诺思格</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="D66" t="n">
-        <v>-0.46</v>
-      </c>
-      <c r="E66" t="n">
-        <v>67.28</v>
-      </c>
-      <c r="F66" t="n">
-        <v>66.25</v>
-      </c>
-      <c r="G66" t="n">
-        <v>63.38</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.063</v>
-      </c>
-      <c r="I66" t="n">
-        <v>-0.9360000000000001</v>
-      </c>
-      <c r="J66" t="n">
-        <v>62.92</v>
-      </c>
-      <c r="K66" t="n">
-        <v>64.67</v>
-      </c>
-      <c r="L66" t="n">
-        <v>59.42</v>
-      </c>
-      <c r="M66" t="n">
-        <v>58.21</v>
-      </c>
-      <c r="N66" t="n">
-        <v>54.34</v>
-      </c>
-      <c r="O66" t="n">
-        <v>51.34</v>
-      </c>
-      <c r="P66" t="n">
-        <v>188.36</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>243.66</v>
-      </c>
-      <c r="R66" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="S66" t="n">
-        <v>67.11</v>
-      </c>
-      <c r="T66" t="n">
-        <v>69.09999999999999</v>
-      </c>
-      <c r="U66" t="n">
-        <v>66.92</v>
-      </c>
-      <c r="V66" t="inlineStr"/>
-      <c r="W66" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>963</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>华东医药</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>35.95</v>
-      </c>
-      <c r="D67" t="n">
-        <v>-0.83</v>
-      </c>
-      <c r="E67" t="n">
-        <v>36.26</v>
-      </c>
-      <c r="F67" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="G67" t="n">
-        <v>35.36</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="I67" t="n">
-        <v>-0.082</v>
-      </c>
-      <c r="J67" t="n">
-        <v>74.13</v>
-      </c>
-      <c r="K67" t="n">
-        <v>72.84999999999999</v>
-      </c>
-      <c r="L67" t="n">
-        <v>76.69</v>
-      </c>
-      <c r="M67" t="n">
-        <v>53.39</v>
-      </c>
-      <c r="N67" t="n">
-        <v>53.07</v>
-      </c>
-      <c r="O67" t="n">
-        <v>49.34</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1288.95</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>1105.28</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="S67" t="n">
-        <v>36.09</v>
-      </c>
-      <c r="T67" t="n">
-        <v>36.43</v>
-      </c>
-      <c r="U67" t="n">
-        <v>35.66</v>
-      </c>
-      <c r="V67" t="inlineStr"/>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>603658</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>安图生物</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="D68" t="n">
-        <v>-1.52</v>
-      </c>
-      <c r="E68" t="n">
-        <v>34.49</v>
-      </c>
-      <c r="F68" t="n">
-        <v>33.99</v>
-      </c>
-      <c r="G68" t="n">
-        <v>34.11</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-0.252</v>
-      </c>
-      <c r="I68" t="n">
-        <v>-0.455</v>
-      </c>
-      <c r="J68" t="n">
-        <v>79.28</v>
-      </c>
-      <c r="K68" t="n">
-        <v>70.56999999999999</v>
-      </c>
-      <c r="L68" t="n">
-        <v>96.68000000000001</v>
-      </c>
-      <c r="M68" t="n">
-        <v>54.26</v>
-      </c>
-      <c r="N68" t="n">
-        <v>50.21</v>
-      </c>
-      <c r="O68" t="n">
-        <v>46.69</v>
-      </c>
-      <c r="P68" t="n">
-        <v>177.53</v>
-      </c>
-      <c r="Q68" t="n">
-        <v>200.93</v>
-      </c>
-      <c r="R68" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="S68" t="n">
-        <v>34.77</v>
-      </c>
-      <c r="T68" t="n">
-        <v>35.12</v>
-      </c>
-      <c r="U68" t="n">
-        <v>34.4</v>
-      </c>
-      <c r="V68" t="inlineStr"/>
-      <c r="W68" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>300357</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>我武生物</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>26.18</v>
-      </c>
-      <c r="D69" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="E69" t="n">
-        <v>25.96</v>
-      </c>
-      <c r="F69" t="n">
-        <v>25.71</v>
-      </c>
-      <c r="G69" t="n">
-        <v>25.27</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I69" t="n">
-        <v>-0.291</v>
-      </c>
-      <c r="J69" t="n">
-        <v>75.75</v>
-      </c>
-      <c r="K69" t="n">
-        <v>72.17</v>
-      </c>
-      <c r="L69" t="n">
-        <v>82.92</v>
-      </c>
-      <c r="M69" t="n">
-        <v>62.2</v>
-      </c>
-      <c r="N69" t="n">
-        <v>55.63</v>
-      </c>
-      <c r="O69" t="n">
-        <v>49.34</v>
-      </c>
-      <c r="P69" t="n">
-        <v>1324.23</v>
-      </c>
-      <c r="Q69" t="n">
-        <v>1198.95</v>
-      </c>
-      <c r="R69" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="S69" t="n">
-        <v>25.76</v>
-      </c>
-      <c r="T69" t="n">
-        <v>26.88</v>
-      </c>
-      <c r="U69" t="n">
-        <v>25.66</v>
-      </c>
-      <c r="V69" t="inlineStr"/>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>2026-04-09</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>688050</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>爱博医疗</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>51.17</v>
-      </c>
-      <c r="D70" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="E70" t="n">
-        <v>51.52</v>
-      </c>
-      <c r="F70" t="n">
-        <v>51.62</v>
-      </c>
-      <c r="G70" t="n">
-        <v>52.4</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-1.574</v>
-      </c>
-      <c r="I70" t="n">
-        <v>-1.842</v>
-      </c>
-      <c r="J70" t="n">
-        <v>57.59</v>
-      </c>
-      <c r="K70" t="n">
-        <v>54.83</v>
-      </c>
-      <c r="L70" t="n">
-        <v>63.11</v>
-      </c>
-      <c r="M70" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="N70" t="n">
-        <v>39.53</v>
-      </c>
-      <c r="O70" t="n">
-        <v>38.16</v>
-      </c>
-      <c r="P70" t="n">
-        <v>126.39</v>
-      </c>
-      <c r="Q70" t="n">
-        <v>165.68</v>
-      </c>
-      <c r="R70" t="n">
-        <v>0.76</v>
-      </c>
-      <c r="S70" t="n">
-        <v>52.56</v>
-      </c>
-      <c r="T70" t="n">
-        <v>52.56</v>
-      </c>
-      <c r="U70" t="n">
-        <v>51.16</v>
-      </c>
-      <c r="V70" t="inlineStr"/>
-      <c r="W70" t="inlineStr">
         <is>
           <t>2026-04-09</t>
         </is>
